--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0013.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0013.xlsx
@@ -1047,16 +1047,16 @@
 Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
-Tiêu hao STA để thực hiện Đòn Hạ Cánh, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau đó để tung ra &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
+Tiêu hao STA để thực hiện Đòn Hạ Cánh, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau đó để tung ra &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thực hiện đòn này để tung ra &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thực hiện đòn này để tung ra &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Wide Field Observation Mode&lt;/color&gt;&lt;/size&gt;
 Khi ở trong &lt;color=Highlight&gt;&lt;te href=120902&gt;Wide Field Observation Mode&lt;/te&gt;&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Dodge Counter - Wide Field Observation Mode&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để phản công và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Trong khoảng thời gian nhất định sau đó, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Basic Attack - Wide Field Observation Mode Stage 3&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để phản công và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+Trong khoảng thời gian nhất định sau đó, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Basic Attack - Wide Field Observation Mode Stage 3&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
 Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
 Nếu không bị tấn công trong trạng thái Phản Đòn, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để thoát trạng thái và tung ra &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Optimal Solution&lt;/color&gt;&lt;/size&gt;
-Gây Trì Trệ cho mục tiêu gần đó và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, đồng thời giảm Cooldown chiêu của &lt;color=Highlight&gt;Resonance Skill - Expectation Error&lt;/color&gt; đi {0}s.
+Gây Trì Trệ cho mục tiêu gần đó và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, đồng thời giảm Thời gian hồi chiêu của &lt;color=Highlight&gt;Resonance Skill - Expectation Error&lt;/color&gt; đi {0}s.
 Việc chuyển đổi sang Resonators khác sẽ kết thúc hiệu ứng Trì Trệ sớm.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Distributed Array&lt;/color&gt;&lt;/size&gt;
@@ -1299,7 +1299,7 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Ground Resonance Skill&lt;/color&gt;&lt;/size&gt;
-Heal HP cho tất cả Resonators gần đó và bước vào trạng thái đỡ đòn trong một khoảng thời gian. Khi đỡ đòn thành công, phản công mục tiêu và giảm Cooldown chiêu của &lt;color=Highlight&gt;Resonance Skill – Expectation Error&lt;/color&gt;.
+Heal HP cho tất cả Resonators gần đó và bước vào trạng thái đỡ đòn trong một khoảng thời gian. Khi đỡ đòn thành công, phản công mục tiêu và giảm Thời gian hồi chiêu của &lt;color=Highlight&gt;Resonance Skill – Expectation Error&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Resonance Skill&lt;/color&gt;&lt;/size&gt;
 Khi ở &lt;color=Highlight&gt;Hovering Mode&lt;/color&gt;, Resonance Skill sẽ được thay thế bằng &lt;color=Highlight&gt;Mid-air Resonance Skill&lt;/color&gt;.
@@ -1995,8 +1995,8 @@
 - Nếu &lt;color=Highlight&gt;&lt;te href=120904&gt;Relative Momentum&lt;/te&gt;&lt;/color&gt; dưới {0} khi giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt;, thực hiện &lt;color=Highlight&gt;Basic Attack - Stage 1 đến 3 Wide Field Observation Mode&lt;/color&gt; theo thứ tự. Nếu &lt;color=Highlight&gt;&lt;te href=120904&gt;Relative Momentum&lt;/te&gt;&lt;/color&gt; đạt {0} trong lúc này, thay vào đó sẽ thực hiện &lt;color=Highlight&gt;Heavy Attack - Đảo Chiều&lt;/color&gt;.
 - Khi di chuyển, Mornye liên tục tiêu hao STA. STA không thể hồi phục trong &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt;.
 - Khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; có nhập hướng, Mornye sẽ bắt đầu bay với tốc độ cao, kéo dài tối đa 10 giây hoặc cho đến khi STA cạn kiệt hoặc &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt; kết thúc.
-- Khi Mornye bị tấn công hoặc bị hất tung lên không trung, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; để hồi phục ngay lập tức khỏi đòn tấn công, được tính là Dodge thành công. Hiệu ứng này có thể kích hoạt tối đa {12} lần và sẽ được đặt lại khi &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt; kết thúc.
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy và Mornye sẽ từ từ hạ xuống. Trước khi cô ấy chạm đất, &lt;color=Highlight&gt;Basic Attack - Wide Field Observation Mode&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Mảng Phân Phối&lt;/color&gt; và &lt;color=Highlight&gt;Heavy Attack - Đảo Chiều&lt;/color&gt; sẽ không khả dụng. Nếu Nhảy được {Cus:Ipt,Touch=tapped PC=pressed Gamepad=pressed} khi Mornye hết STA, cô ấy sẽ thoát khỏi &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt;. Cô ấy cũng sẽ rời khỏi chế độ này khi &lt;color=Highlight&gt;Dodge&lt;/color&gt;, Nhảy hoặc thực hiện Đòn Mid-air Attack.
+- Khi Mornye bị tấn công hoặc bị hất tung lên không trung, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; để hồi phục ngay lập tức khỏi đòn tấn công, được tính là Dodge thành công. Hiệu ứng này có thể kích hoạt tối đa {12} lần và sẽ được đặt lại khi &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt; kết thúc.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Nhảy và Mornye sẽ từ từ hạ xuống. Trước khi cô ấy chạm đất, &lt;color=Highlight&gt;Basic Attack - Wide Field Observation Mode&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Mảng Phân Phối&lt;/color&gt; và &lt;color=Highlight&gt;Heavy Attack - Đảo Chiều&lt;/color&gt; sẽ không khả dụng. Nếu Nhảy được {Cus:Ipt,Touch=tapped PC=pressed Gamepad=pressed} khi Mornye hết STA, cô ấy sẽ thoát khỏi &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt;. Cô ấy cũng sẽ rời khỏi chế độ này khi &lt;color=Highlight&gt;Dodge&lt;/color&gt;, Nhảy hoặc thực hiện Đòn Mid-air Attack.
 Ngoài ra, thực hiện tương tác với môi trường, sử dụng Tiện Ích hoặc chuyển đổi sang Resonators khác sẽ kết thúc &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt;. Trạng thái này cũng kết thúc khi Mornye không còn ở trên không.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Trường Resonance&lt;/color&gt;&lt;/size&gt;
@@ -2657,13 +2657,13 @@
       <c r="M28" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} hoặc giữ Normal Attack để thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} hoặc giữ Normal Attack để thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để thực hiện Plunging Attack, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Spark Collision&lt;/color&gt;&lt;/size&gt;
 Khi &lt;color=Highlight&gt;&lt;te href=150905&gt;Overflow&lt;/te&gt;&lt;/color&gt; trong &lt;color=Highlight&gt;&lt;te href=150901&gt;Optical Sampling Stage&lt;/te&gt;&lt;/color&gt; đạt tối đa, giữ Normal Attack để vào trạng thái sạc.
@@ -2691,8 +2691,8 @@
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Kaleidoscopic Parade - Dodge Counter&lt;/color&gt;&lt;/size&gt;
 Khi ở trong &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Kaleidoscopic Parade - Dodge Counter&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Khi ở trong &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack Stage 2&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
+Khi ở trong &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack Stage 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2842,15 +2842,15 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Lynae-Style Palettes&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. 
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Skill để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. 
 Trong trạng thái &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;, giữ Resonance Skill để tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và thoát khỏi &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;. 
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack trong một khoảng thời gian nhất định sau khi sử dụng kỹ năng này để thi triển &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
-Bảng Màu Lynae và Cộng Màu &lt;color=Highlight&gt;share a cooldown&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack trong một khoảng thời gian nhất định sau khi sử dụng kỹ năng này để thi triển &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
+Bảng Màu Lynae và Cộng Màu &lt;color=Highlight&gt;share a thời gian hồi&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Additive Color&lt;/color&gt;&lt;/size&gt;
-Trong trạng thái &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill trên mặt đất để tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Trong một khoảng thời gian nhất định khi sử dụng kỹ năng, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để thi triển &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack Stage 2&lt;/color&gt;.
-Bảng Màu Lynae và Cộng Màu &lt;color=Highlight&gt;share a cooldown&lt;/color&gt;.</t>
+Trong trạng thái &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Skill trên mặt đất để tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
+Trong một khoảng thời gian nhất định khi sử dụng kỹ năng, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack để thi triển &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack Stage 2&lt;/color&gt;.
+Bảng Màu Lynae và Cộng Màu &lt;color=Highlight&gt;share a thời gian hồi&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2995,8 +2995,8 @@
           <t>Gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Khi sử dụng kỹ năng này, tăng {0} sát thương cho tất cả Resonators gần đó trong đội trong {1} giây.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Basic Attack - To a Vivid Tomorrow!&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack trong khoảng thời gian nhất định sau khi sử dụng &lt;color=Highlight&gt;Resonance Liberation - Prismatic Overblast&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Basic Attack - To a Vivid Tomorrow!&lt;/color&gt;, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Khi ở trạng thái &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack trong khoảng thời gian nhất định để thi triển &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack Stage 2&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack trong khoảng thời gian nhất định sau khi sử dụng &lt;color=Highlight&gt;Resonance Liberation - Prismatic Overblast&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Basic Attack - To a Vivid Tomorrow!&lt;/color&gt;, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
+Khi ở trạng thái &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack trong khoảng thời gian nhất định để thi triển &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack Stage 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
           <t>Kích hoạt kỹ năng này sẽ tăng Sát Thương gây ra bởi tất cả Resonators trong đội ở gần.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Motorbike Chain Attack&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack trong khoảng thời gian nhất định sau khi kích hoạt &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để thực hiện đòn tấn công xích bằng xe máy.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack trong khoảng thời gian nhất định sau khi kích hoạt &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để thực hiện đòn tấn công xích bằng xe máy.</t>
         </is>
       </c>
     </row>
@@ -3600,18 +3600,18 @@
 Trong trạng thái &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;, khi &lt;color=Highlight&gt;&lt;te href=150906&gt;Lumiflow&lt;/te&gt;&lt;/color&gt; đạt ít nhất 1/3 tối đa, Nhảy sẽ được thay thế bằng &lt;color=Highlight&gt;Basic Attack - Polychrome Leap&lt;/color&gt;.
 Tiêu hao 1/3 tối đa &lt;color=Highlight&gt;&lt;te href=150906&gt;Lumiflow&lt;/te&gt;&lt;/color&gt; để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Gây hiệu ứng &lt;color=Highlight&gt;&lt;te href=150903&gt;Photochromic Flux&lt;/te&gt;&lt;/color&gt; lên mục tiêu trúng đòn. Có thể kích hoạt Dodge Thành Công trong một khoảng thời gian nhất định khi sử dụng kỹ năng này. Khi ở trên không, &lt;color=Highlight&gt;Basic Attack - Polychrome Leap&lt;/color&gt; có thể thực hiện tối đa 3 giai đoạn. Switch đổi sang Resonators khác sẽ đặt lại chuỗi kỹ năng.
 Trong chiến đấu, mỗi giai đoạn của &lt;color=Highlight&gt;Basic Attack - Polychrome Leap&lt;/color&gt; sẽ hồi phục 1 điểm &lt;color=Highlight&gt;&lt;te href=150907&gt;True Color&lt;/te&gt;&lt;/color&gt;.
-Trong một khoảng thời gian nhất định sau khi sử dụng &lt;color=Highlight&gt;Basic Attack - Polychrome Leap Stage 1&lt;/color&gt; {Cus:Ipt,Touch=tap PC=press Gamepad=press} Kỹ Năng Thường trên mặt đất để thực hiện &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack Stage 2&lt;/color&gt;.
+Trong một khoảng thời gian nhất định sau khi sử dụng &lt;color=Highlight&gt;Basic Attack - Polychrome Leap Stage 1&lt;/color&gt; {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Kỹ Năng Thường trên mặt đất để thực hiện &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack Stage 2&lt;/color&gt;.
 Sử dụng &lt;color=Highlight&gt;Basic Attack - Polychrome Leap Stage 2&lt;/color&gt; cũng sẽ hút các mục tiêu gần đó.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Iridescent Splash&lt;/color&gt;&lt;/size&gt;
-Trong trạng thái &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;, khi Lynae ở trên không với 3 điểm &lt;color=Highlight&gt;&lt;te href=150907&gt;True Color&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;Basic Attack - Visual Impact&lt;/color&gt; đang Cooldown, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Kỹ Năng Thường hoặc Resonance Skill để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và gây hiệu ứng &lt;color=Highlight&gt;&lt;te href=150903&gt;Photochromic Flux&lt;/te&gt;&lt;/color&gt; lên mục tiêu trúng đòn.
+Trong trạng thái &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;, khi Lynae ở trên không với 3 điểm &lt;color=Highlight&gt;&lt;te href=150907&gt;True Color&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;Basic Attack - Visual Impact&lt;/color&gt; đang Thời gian hồi, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Kỹ Năng Thường hoặc Resonance Skill để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và gây hiệu ứng &lt;color=Highlight&gt;&lt;te href=150903&gt;Photochromic Flux&lt;/te&gt;&lt;/color&gt; lên mục tiêu trúng đòn.
 Skill này tiêu hao 3 điểm &lt;color=Highlight&gt;&lt;te href=150907&gt;True Color&lt;/te&gt;&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Kỹ Năng Thường trong một khoảng thời gian nhất định khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Kỹ Năng Thường trong một khoảng thời gian nhất định khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Visual Impact&lt;/color&gt;&lt;/size&gt;
-Trong trạng thái &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;, khi Lynae ở trên không với 3 điểm &lt;color=Highlight&gt;&lt;te href=150907&gt;True Color&lt;/te&gt;&lt;/color&gt; và kỹ năng này không Cooldown, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Kỹ Năng Thường hoặc Resonance Skill để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và gây hiệu ứng &lt;color=Highlight&gt;&lt;te href=150903&gt;Photochromic Flux&lt;/te&gt;&lt;/color&gt; lên mục tiêu trúng đòn.
+Trong trạng thái &lt;color=Highlight&gt;&lt;te href=150902&gt;Kaleidoscopic Parade&lt;/te&gt;&lt;/color&gt;, khi Lynae ở trên không với 3 điểm &lt;color=Highlight&gt;&lt;te href=150907&gt;True Color&lt;/te&gt;&lt;/color&gt; và kỹ năng này không Thời gian hồi, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Kỹ Năng Thường hoặc Resonance Skill để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và gây hiệu ứng &lt;color=Highlight&gt;&lt;te href=150903&gt;Photochromic Flux&lt;/te&gt;&lt;/color&gt; lên mục tiêu trúng đòn.
 Skill này tiêu hao 3 điểm &lt;color=Highlight&gt;&lt;te href=150907&gt;True Color&lt;/te&gt;&lt;/color&gt; và cấp cho tất cả Resonators trong đội gần đó {0} điểm Tăng Cường Phá Vỡ Giai Tune trong {1} giây.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Kỹ Năng Thường trong một khoảng thời gian nhất định khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Kỹ Năng Thường trong một khoảng thời gian nhất định khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Mode&lt;/color&gt;&lt;/size&gt;
 Gây hiệu ứng &lt;color=Highlight&gt;&lt;te href=150903&gt;Photochromic Flux&lt;/te&gt;&lt;/color&gt; khi trúng mục tiêu bằng &lt;color=Highlight&gt;Basic Attack - Polychrome Leap&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Iridescent Splash&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Visual Impact&lt;/color&gt; và &lt;color=Highlight&gt;Intro Skill - Time to Show Some Colors!&lt;/color&gt;.
@@ -3732,7 +3732,7 @@
 Trong &lt;color=Highlight&gt;Roller Skating Mode&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy và tiêu hao 1/3 &lt;color=Highlight&gt;Lumiflow&lt;/color&gt; tối đa để thực hiện đòn nhảy tấn công, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Gây hiệu ứng &lt;color=Highlight&gt;Photochromic Flux&lt;/color&gt; lên mục tiêu trúng đòn. Có thể thực hiện liên tiếp tối đa 3 lần.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Roller Skate Plunge Chain Attack&lt;/color&gt;&lt;/size&gt;
-Trong &lt;color=Highlight&gt;Roller Skating Mode&lt;/color&gt;, khi đang ở trên không với &lt;color=Highlight&gt;True Color&lt;/color&gt; tối đa, nếu &lt;color=Highlight&gt;Enhanced Roller Skate Plunge Attack&lt;/color&gt; không trong Cooldown chiêu, hãy sử dụng &lt;color=Highlight&gt;Enhanced Roller Skate Plunge Attack&lt;/color&gt;, nếu không thì thay bằng &lt;color=Highlight&gt;Roller Skate Plunge Attack&lt;/color&gt;. Gây hiệu ứng &lt;color=Highlight&gt;Photochromic Flux&lt;/color&gt; lên mục tiêu trúng đòn.
+Trong &lt;color=Highlight&gt;Roller Skating Mode&lt;/color&gt;, khi đang ở trên không với &lt;color=Highlight&gt;True Color&lt;/color&gt; tối đa, nếu &lt;color=Highlight&gt;Enhanced Roller Skate Plunge Attack&lt;/color&gt; không trong Thời gian hồi chiêu, hãy sử dụng &lt;color=Highlight&gt;Enhanced Roller Skate Plunge Attack&lt;/color&gt;, nếu không thì thay bằng &lt;color=Highlight&gt;Roller Skate Plunge Attack&lt;/color&gt;. Gây hiệu ứng &lt;color=Highlight&gt;Photochromic Flux&lt;/color&gt; lên mục tiêu trúng đòn.
 Sử dụng &lt;color=Highlight&gt;Enhanced Roller Skate Plunge Attack&lt;/color&gt; sẽ tăng hiệu ứng Tăng Cường Vỡ Nhịp cho tất cả Resonators trong đội ở gần.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Mode&lt;/color&gt;&lt;/size&gt;
@@ -4240,15 +4240,15 @@
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
 Thực hiện tối đa 4 đòn tấn công liên tiếp trên không, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Stage 4 là Đòn Lao Xuống tiêu hao STA.
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nhảy&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; Giai Đoạn {0} và 3 trên không.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nhảy&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; Giai Đoạn {0} và 3 trên không.
 Luuk Herssen tấn công bằng &lt;color=Highlight&gt;Scythe: Dissection&lt;/color&gt; khi nhập lệnh &lt;color=Highlight&gt;Normal Attack&lt;/color&gt;.
 Luuk Herssen tấn công bằng &lt;color=Highlight&gt;Scythe: Resection&lt;/color&gt; khi nhập lệnh &lt;color=Highlight&gt;Nhảy&lt;/color&gt;. Hắn cũng gây &lt;color=Highlight&gt;&lt;te href=100003&gt;Tune Strain - Shifting&lt;/te&gt;&lt;/color&gt; lên mục tiêu trúng đòn trong {1} giây và giảm sát thương nhận vào {3} trong {2} giây.
 Khi là Resonator chủ động, chu kỳ kỹ năng này trên không sẽ không bị reset.
 Khi ở trên không, &lt;color=Highlight&gt;giữ Normal Attack&lt;/color&gt; để thực hiện Đòn Lao Xuống tiêu hao STA.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công trên mặt đất để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công trên không để lao về phía mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công trên mặt đất để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công trên không để lao về phía mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
 &lt;color=Highlight&gt;Giữ Normal Attack&lt;/color&gt; để thực hiện Đòn Lao Xuống, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press}&lt;/color&gt; &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press}&lt;/color&gt; &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       <c r="M58" t="inlineStr">
         <is>
           <t>Gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Dodgem một lưỡi &lt;color=Highlight&gt;&lt;te href=151004&gt;Ichor Blade&lt;/te&gt;&lt;/color&gt; và gây hiệu ứng &lt;color=Highlight&gt;&lt;te href=100003&gt;Tune Strain - Shifting&lt;/te&gt;&lt;/color&gt; lên mục tiêu.
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; sau kỹ năng này để thi triển &lt;color=Highlight&gt;Mid-air Attack Stage 2 - Scythe: Dissection&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nhảy&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Mid-air Attack Stage 2 - Scythe: Resection&lt;/color&gt;.</t>
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; sau kỹ năng này để thi triển &lt;color=Highlight&gt;Mid-air Attack Stage 2 - Scythe: Dissection&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nhảy&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Mid-air Attack Stage 2 - Scythe: Resection&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>Gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và áp dụng &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt;.
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack or Nhảy&lt;/color&gt; sau khi sử dụng kỹ năng này để thi triển &lt;color=Highlight&gt;Mid-air Attack Stage 2&lt;/color&gt;.</t>
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack or Nhảy&lt;/color&gt; sau khi sử dụng kỹ năng này để thi triển &lt;color=Highlight&gt;Mid-air Attack Stage 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
 Một số kỹ năng sẽ hồi phục &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt;. Khi &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; đầy, hệ số Sát Thương của tất cả &lt;color=Highlight&gt;Enhanced Resonance Skills&lt;/color&gt; sẽ tăng lên.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Golden Rule&lt;/color&gt;&lt;/size&gt;
-Khi Resonators khác trong đội sử dụng Outro Skill và Luuk Herssen là Resonators tiếp theo, cậu ta sẽ hồi phục thêm &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; và Concerto Energy. Hiệu ứng này có Cooldown {0}s.
+Khi Resonators khác trong đội sử dụng Outro Skill và Luuk Herssen là Resonators tiếp theo, cậu ta sẽ hồi phục thêm &lt;color=Highlight&gt;Forte Gauge&lt;/color&gt; và Concerto Energy. Hiệu ứng này có Thời gian hồi {0}s.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dawnlit Keep&lt;/color&gt;&lt;/size&gt;
 Luuk Herssen nhận được {2} lớp &lt;color=Highlight&gt;Dawnlit Keep&lt;/color&gt; khi không tham chiến quá {1}s hoặc sử dụng Intro Skill, giúp giảm Sát Thương nhận vào và miễn nhiễm với hiệu ứng gián đoạn trong một khoảng thời gian.
@@ -5641,7 +5641,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Dòng "Vũ Khí Tổng Hợp" của Spacetrek Collective
+          <t>Dòng "Vũ Khí Tổng Hợp" của Tập Đoàn Spacetrek
 Mẫu: SCSA-LHRi-BB325042
 Được rèn từ công nghệ phức hợp kết hợp các thành phần sinh học Exostrider với Tacetite, vũ khí này sở hữu hai đặc tính cốt lõi: tự điều chỉnh tần số và liên kết với người sử dụng. Sức mạnh của nó tỷ lệ thuận với Forte của người sử dụng, trở nên sắc bén hơn qua quá trình rèn luyện Forte chuyên sâu.
 Các hoa văn ánh sáng dọc lưỡi kiếm thay đổi theo sự dao động tần số của người sử dụng. Nó kết tinh lý trí thành một sức mạnh tập trung—vừa là công cụ để phá vỡ chướng ngại, vừa là thước đo để khám phá những điều chưa biết. Hoàn hảo cho những kẻ phá vỡ giới hạn, những người tự khắc họa con đường bằng ý chí kiên định.</t>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Tăng Tấn Công thêm {0}. Gây sát thương lên mục tiêu trong trạng thái Căng Nhịp - Giao Thoa sẽ tăng {1} Sát Thương Resonance Liberation trong {2} giây. Kích hoạt lại sẽ làm mới thời gian hiệu ứng.</t>
+          <t>Tăng ATK thêm {0}. Gây sát thương lên mục tiêu trong trạng thái Căng Nhịp - Giao Thoa sẽ tăng {1} Sát Thương Resonance Liberation trong {2} giây. Kích hoạt lại sẽ làm mới thời gian hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Dòng "Vũ Khí Tổng Hợp" của Spacetrek Collective
+          <t>Dòng "Vũ Khí Tổng Hợp" của Tập Đoàn Spacetrek
 Mẫu: SCSA-LHRi-BB325042
 Được rèn từ công nghệ phức hợp kết hợp các thành phần sinh học Exostrider với Tacetite, vũ khí này sở hữu hai đặc tính cốt lõi: tự điều chỉnh tần số và liên kết với người sử dụng. Sức mạnh của nó tỷ lệ thuận với Forte của người sử dụng, trở nên sắc bén hơn qua quá trình rèn luyện Forte chuyên sâu.
 Các hoa văn ánh sáng dọc lưỡi kiếm thay đổi theo sự dao động tần số của người sử dụng. Nó kết tinh lý trí thành một sức mạnh tập trung—vừa là công cụ để phá vỡ chướng ngại, vừa là thước đo để khám phá những điều chưa biết. Hoàn hảo cho những kẻ phá vỡ giới hạn, những người tự khắc họa con đường bằng ý chí kiên định.</t>
@@ -5846,8 +5846,8 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Tấn Công tăng thêm {0}. Khi người sử dụng thi triển Kỹ Năng Giới Thiệu hoặc gây Trạng Thái Tiêu Cực, họ nhận thêm {1} Sát Thương Resonance Liberation, có thể tích lũy tối đa {2} lần trong {3} giây.
-Khi đạt tối đa lượt tích lũy, nếu Resonators trong đội gây Trạng Thái Tiêu Cực, họ sẽ nhận thêm {4} Tăng Sát Thương Toàn Thuộc Tính trong {5} giây. Hiệu ứng cùng tên không thể chồng chất.</t>
+          <t>ATK tăng thêm {0}. Khi người sử dụng thi triển Kỹ Năng Giới Thiệu hoặc gây Trạng Thái Tiêu Cực, họ nhận thêm {1} Sát Thương Resonance Liberation, có thể tích lũy tối đa {2} lần trong {3} giây.
+Khi đạt tối đa lượt tích lũy, nếu Resonator trong đội gây Trạng Thái Tiêu Cực, họ sẽ nhận thêm {4} Tăng Sát Thương Toàn Thuộc Tính trong {5} giây. Hiệu ứng cùng tên không thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Tăng Phòng Ngự thêm {0}. Khi sử dụng Resonance Skill sẽ khôi phục {1} điểm Concerto Energy. Hiệu ứng này có thể kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi {2} giây. Khi người sử dụng hồi máu cho Resonators, tăng Crit. DMG cho tất cả Resonators gần đó trong đội thêm {4} trong {5} giây. Các hiệu ứng cùng tên không thể chồng chất.</t>
+          <t>Tăng Phòng Ngự thêm {0}. Khi sử dụng Resonance Skill sẽ khôi phục {1} điểm Concerto Energy. Hiệu ứng này có thể kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi {2} giây. Khi người sử dụng hồi máu cho Resonator, tăng Crit. DMG cho tất cả Resonator gần đó trong đội thêm {4} trong {5} giây. Các hiệu ứng cùng tên không thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tăng Attack {0} và tăng {1} Sát Thương Kỹ Năng Nặng trong {2} giây.</t>
+          <t>Kích hoạt Giải Cứu Cộng Hưởng tăng ATK {0} và tăng {1} Sát Thương Kỹ Năng Nặng trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Tăng Tấn Công thêm {0}. Gây sát thương lên mục tiêu trong trạng thái Căng Nhịp - Giao Thoa sẽ tăng {1} Sát Thương Resonance Skill trong {2} giây. Kích hoạt lại sẽ làm mới thời gian hiệu ứng.</t>
+          <t>Tăng ATK thêm {0}. Gây sát thương lên mục tiêu trong trạng thái Căng Nhịp - Giao Thoa sẽ tăng {1} Sát Thương Resonance Skill trong {2} giây. Kích hoạt lại sẽ làm mới thời gian hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -6250,8 +6250,8 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Attack tăng {0}. Khi sử dụng Kỹ Năng Echoes trong vòng {1} giây sau khi dùng Intro Skill hoặc Basic Attack, nhận 1 tầng Bamboo Cleaver, tăng {2}% Sát Thương Heavy Attack cho người sử dụng. Hiệu ứng này chỉ có thể kích hoạt bởi Echoes cùng tên một lần, tối đa 2 tầng, kéo dài {3} giây. Sử dụng Kỹ Năng Echoes ở tối đa tầng không làm reset thời gian. Hiệu ứng này có thể kích hoạt mỗi {4} giây và sẽ kết thúc sớm nếu người sử dụng rời khỏi chiến trường.
-Sử dụng Intro Skill sẽ tăng {5} Sát Thương Kỹ Năng Echoes cho tất cả Resonators trong đội trong {6} giây. Hiệu ứng cùng tên không thể cộng dồn.</t>
+          <t>ATK tăng {0}. Khi sử dụng Kỹ Năng Echo trong vòng {1} giây sau khi dùng Kỹ Năng Intro hoặc Đòn Cơ Bản, nhận 1 tầng Bamboo Cleaver, tăng {2}% Sát Thương Đòn Nặng cho người sử dụng. Hiệu ứng này chỉ có thể kích hoạt bởi Echo cùng tên một lần, tối đa 2 tầng, kéo dài {3} giây. Sử dụng Kỹ Năng Echo ở tối đa tầng không làm reset thời gian. Hiệu ứng này có thể kích hoạt mỗi {4} giây và sẽ kết thúc sớm nếu người sử dụng rời khỏi chiến trường.
+Sử dụng Kỹ Năng Intro sẽ tăng {5} Sát Thương Kỹ Năng Echo cho tất cả Resonator trong đội trong {6} giây. Hiệu ứng cùng tên không thể cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Attack tăng {0}. Khi gây Sát Thương Kỹ Năng Echo, nhận {1} DMG Amplification Heavy Attack trong {2} giây. Khi gây Sát Thương Heavy Attack, nhận {3} DMG Amplification Kỹ Năng Echo trong {4} giây. DMG Amplification mỗi đòn tối đa là {5}. Khi cả hai hiệu ứng cùng hoạt động, gây sát thương sẽ bỏ qua {6} Phòng Ngự của mục tiêu.</t>
+          <t>ATK tăng {0}. Khi gây Sát Thương Kỹ Năng Echo, nhận {1} Khuếch Đại Sát Thương Đòn Nặng trong {2} giây. Khi gây Sát Thương Đòn Nặng, nhận {3} Khuếch Đại Sát Thương Kỹ Năng Echo trong {4} giây. Khuếch Đại Sát Thương mỗi đòn tối đa là {5}. Khi cả hai hiệu ứng cùng hoạt động, gây DMG sẽ bỏ qua {6} Phòng Ngự của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Increases ATK by {0}. Sau khi một Resonator trong đội sử dụng kỹ năng Tune Break, sẽ tăng {1} Sát Thương Thuộc Tính cho người sử dụng trong {2} giây.</t>
+          <t>Tăng ATK {0}. Sau khi một Resonator trong đội sử dụng kỹ năng Tune Break, sẽ tăng {1} Sát Thương Thuộc Tính cho người sử dụng trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Tăng Attack thêm {0}. Sử dụng Intro Skill hoặc gây Sát Thương Basic Attack lên mục tiêu sẽ tăng {1} Sát Thương Basic Attack cho bản thân trong {2} giây. Mỗi lần gây Trạng Thái Vỡ Nhịp - Dịch Chuyển hoặc Căng Nhịp - Dịch Chuyển trong Basic Attack, toàn bộ Resonators trong đội sẽ tăng {3} toàn bộ Sát Thương trong {5} giây, tối đa {4} lớp. Các hiệu ứng cùng tên không thể chồng chất.</t>
+          <t>Tăng ATK thêm {0}. Sử dụng Kỹ Năng Khởi Động hoặc gây Sát Thương Basic Attack lên mục tiêu sẽ tăng {1} Sát Thương Basic Attack cho bản thân trong {2} giây. Mỗi lần gây Trạng Thái Vỡ Nhịp - Dịch Chuyển hoặc Căng Nhịp - Dịch Chuyển trong Basic Attack, toàn bộ Resonator trong đội sẽ tăng {3} toàn bộ Sát Thương trong {5} giây, tối đa {4} lớp. Các hiệu ứng cùng tên không thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Tăng Attack thêm {0}. Gây sát thương lên mục tiêu trong trạng thái Căng Nhịp - Giao Thoa sẽ tăng {1} Sát Thương Basic Attack trong {2} giây, tối đa {3} lớp. Hiệu ứng kích hoạt &lt;SapTag=5&gt;{5}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=5} mỗi {4} giây. Kích hoạt lại sẽ làm mới thời gian hiệu ứng.</t>
+          <t>Tăng ATK thêm {0}. Gây DMG lên mục tiêu trong trạng thái Căng Nhịp - Giao Thoa sẽ tăng {1} Sát Thương Basic Attack trong {2} giây, tối đa {3} lớp. Hiệu ứng kích hoạt &lt;SapTag=5&gt;{5}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=5} mỗi {4} giây. Kích hoạt lại sẽ làm mới thời gian hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Increase Attack {0}. Sau khi một Resonator trong đội sử dụng kỹ năng Tune Break, sẽ tăng thêm {1} Attack và {2} Sát Thương Basic Attack cho người sử dụng trong {3} giây.</t>
+          <t>Tăng ATK {0}. Sau khi một Resonator trong đội sử dụng kỹ năng Tune Break, sẽ tăng thêm {1} ATK và {2} Sát Thương Đòn Basic Attack cho người sử dụng trong {3} giây.</t>
         </is>
       </c>
     </row>
@@ -7202,8 +7202,8 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Summon Dwarf Cassowary truy đuổi và tấn công kẻ địch, gây {1} Sát Thương Physical {0} lần.
-Hồi chiêu: {2} giây</t>
+          <t>Triệu hồi Dwarf Cassowary truy đuổi và tấn công kẻ địch, gây {1} Sát Thương Vật Lý {0} lần.
+Thời gian hồi: {2} giây</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Summon Dwarf Cassowary tấn công, gây Sát Thương Physical.</t>
+          <t>Triệu hồi Dwarf Cassowary tấn công, gây Sát Thương Vật Lý.</t>
         </is>
       </c>
     </row>
@@ -7335,9 +7335,9 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Tiến lên như một Lightcrusher, gây {0} Spectro DMG. Khi trúng mục tiêu, tạo ra {1} Ablucence. Mỗi vụ nổ Ablucence gây {2} Spectro DMG.
+          <t>Tiến lên như một Lightcrusher, gây {0} Sát Thương Spectro. Khi trúng mục tiêu, tạo ra {1} Ablucence. Mỗi vụ nổ Ablucence gây {2} Sát Thương Spectro.
 Giữ kỹ năng Echo để duy trì dạng Lightcrusher, cho phép bạn bật lên không trung và phóng về phía trước một đoạn ngắn.
-Hồi chiêu: {3} giây</t>
+Thời gian hồi: {3} giây</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Xông lên dưới dạng Lightcrusher, gây Spectro DMG.
+          <t>Xông lên dưới dạng Lightcrusher, gây Sát Thương Spectro.
 Giữ Kỹ Năng Echo để tăng đà và lao xa hơn sau khi chuyển hóa thành Lightcrusher.</t>
         </is>
       </c>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Biến thành Lumiscale Construct và vào tư thế Phản Đòn. Nếu không bị tấn công trong tư thế này, khi kết thúc, ngươi sẽ vung kiếm gây {0} Glacio DMG. Nếu bị tấn công, phản đòn ngay lập tức, gây {1} Glacio DMG. Khi bị tấn công bằng &lt;color=Highlight&gt;Special Skill&lt;/color&gt; trong tư thế Phản Đòn, phá vỡ &lt;color=Highlight&gt;Special Skill&lt;/color&gt; đó và phản đòn, gây {1} Glacio DMG.
+          <t>Biến hình thành Lumiscale Construct và vào tư thế Phản Đòn. Nếu không bị tấn công trong tư thế này, khi kết thúc, ngươi sẽ vung kiếm gây {0} Sát Thương Glacio. Nếu bị tấn công, phản đòn ngay lập tức, gây {1} Sát Thương Glacio. Khi bị tấn công bằng &lt;color=Highlight&gt;Kỹ Năng Đặc Biệt&lt;/color&gt; trong tư thế Phản Đòn, phá vỡ &lt;color=Highlight&gt;Kỹ Năng Đặc Biệt&lt;/color&gt; đó và phản đòn, gây {1} Sát Thương Glacio.
 Hồi chiêu: {2} giây</t>
         </is>
       </c>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Biến thành Lumiscale Construct và vào tư thế Phản Đòn. Khi bị tấn công, thực hiện phản đòn. Nếu đỡ được đòn Kỹ Năng Special, ngắt kỹ năng đó và gây thêm sát thương.</t>
+          <t>Biến hình thành Lumiscale Construct và vào tư thế Phản Đòn. Khi bị tấn công, thực hiện phản đòn. Nếu đỡ được đòn Kỹ Năng Đặc Biệt, ngắt kỹ năng đó và gây thêm sát thương.</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Summon một Lava Larva liên tục tấn công kẻ địch, mỗi đòn gây {0} Fusion DMG. Lava Larva sẽ biến mất khi người triệu hồi bị thay ra hoặc di chuyển quá xa.
+          <t>Triệu hồi một Lava Larva liên tục tấn công kẻ địch, mỗi đòn gây {0} Sát Thương Fusion. Lava Larva sẽ biến mất khi người triệu hồi bị thay ra hoặc di chuyển quá xa.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Summon một Lava Larva liên tục tấn công kẻ địch, gây Fusion DMG.</t>
+          <t>Triệu hồi một Lava Larva liên tục tấn công kẻ địch, gây Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Biến thành Kỵ Sĩ Vô Nhiệm và đập tan kẻ địch xung quanh, gây {0} Electro DMG.
+          <t>Biến hình thành Kỵ Sĩ Vô Nhiệm và đập tan kẻ địch xung quanh, gây {0} Sát Thương Electro.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Biến thành Kỵ Sĩ Vô Nhiệm và gây Electro DMG lên kẻ địch.</t>
+          <t>Biến hình thành Kỵ Sĩ Vô Nhiệm và gây Sát Thương Electro lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Biến thành Kỵ Sĩ Diurnus, lao về phía trước tấn công kẻ địch bằng kiếm, gây {0} Spectro DMG. Sát thương gây ra lên kẻ địch bị Spectro Frazzle tăng thêm {1}.
+          <t>Biến hình thành Kỵ Sĩ Diurnus, lao về phía trước tấn công kẻ địch bằng kiếm, gây {0} Sát Thương Spectro. DMG gây ra lên kẻ địch bị Spectro Frazzle tăng thêm {1}.
 Hồi chiêu: {2} giây.</t>
         </is>
       </c>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Biến thành Kỵ Sĩ Diurnus và gây Spectro DMG lên kẻ địch. Gây sát thương tăng cường lên kẻ địch bị Spectro Frazzle.</t>
+          <t>Biến hình thành Kỵ Sĩ Diurnus và gây Sát Thương Spectro lên kẻ địch. Gây DMG tăng cường lên kẻ địch bị Spectro Frazzle.</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Biến thành Kỵ Sĩ Nocturnus và tấn công kẻ địch phía trước từ trên không, gây {0} Havoc DMG.
+          <t>Biến hình thành Kỵ Sĩ Nocturnus và tấn công kẻ địch phía trước từ trên không, gây {0} Sát Thương Havoc.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Biến thành Kỵ Sĩ Nocturnus và gây Havoc DMG lên kẻ địch.</t>
+          <t>Biến hình thành Kỵ Sĩ Nocturnus và gây Sát Thương Havoc lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -8198,8 +8198,8 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Biến thành Abyssal Gladius và tấn công kẻ địch phía trước bằng kiếm, gây {0} Glacio DMG.
-Giữ Kỹ Năng Echo để duy trì hình dạng Echo trong giây lát, chém kẻ địch và phóng một đòn tấn công tầm xa về phía trước, gây {1} và {2} Glacio DMG tương ứng.
+          <t>Biến hình thành Abyssal Gladius và tấn công kẻ địch phía trước bằng kiếm, gây {0} Sát Thương Glacio.
+Giữ Kỹ Năng Echo để duy trì hình dạng Echo trong giây lát, chém kẻ địch và phóng một đòn tấn công tầm xa về phía trước, gây {1} và {2} Sát Thương Glacio tương ứng.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Biến thành Abyssal Gladius và gây Glacio DMG cho kẻ địch. Giữ Kỹ Năng Echo để phóng đòn tấn công tầm xa gây Glacio DMG.</t>
+          <t>Biến hình thành Abyssal Gladius và gây Sát Thương Glacio cho kẻ địch. Giữ Kỹ Năng Echo để phóng đòn tấn công tầm xa gây Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Biến thành Abyssal Mercator và triệu hồi 3 Cột Băng tấn công kẻ địch, mỗi cột gây {0} Glacio DMG.
+          <t>Biến hình thành Abyssal Mercator và triệu hồi 3 Cột Băng tấn công kẻ địch, mỗi cột gây {0} Sát Thương Glacio.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Biến thành Abyssal Mercator và triệu hồi 3 Cột Băng tấn công kẻ địch, gây Glacio DMG.</t>
+          <t>Biến hình thành Abyssal Mercator và triệu hồi 3 Cột Băng tấn công kẻ địch, gây Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -8464,8 +8464,8 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Biến thành Abyssal Patricius và lao về phía trước tấn công kẻ địch, gây {0} Glacio DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Glacio DMG Bonus.
+          <t>Biến hình thành Abyssal Patricius và lao về phía trước tấn công kẻ địch, gây {0} Sát Thương Glacio.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Tăng Sát Thương Glacio.
 Hồi chiêu: {2} giây.</t>
         </is>
       </c>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Biến thành Abyssal Patricius và gây Glacio DMG cho kẻ địch. Trang bị Echo này ở vị trí chính sẽ nhận Glacio DMG Bonus.</t>
+          <t>Biến hình thành Abyssal Patricius và gây Sát Thương Glacio cho kẻ địch. Trang bị Echo này ở vị trí chính sẽ nhận Tăng Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Summon một Chop Chop thực hiện chuỗi tấn công liên tiếp. 6 đòn đầu mỗi đòn gây {0} Fusion DMG, đòn kết thúc gây {1} Fusion DMG.
+          <t>Triệu hồi một Chop Chop thực hiện chuỗi tấn công liên tiếp. 6 đòn đầu mỗi đòn gây {0} DMG Fusion, đòn kết thúc gây {1} DMG Fusion.
 Hồi chiêu: {2} giây.</t>
         </is>
       </c>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Summon một Chop Chop tung ra loạt đòn tấn công, gây Fusion DMG.</t>
+          <t>Triệu hồi một Chop Chop tung ra loạt đòn tấn công, gây DMG Fusion.</t>
         </is>
       </c>
     </row>
@@ -8730,8 +8730,8 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Biến thành Vitreum Dancer và tấn công kẻ địch xung quanh, gây {0} Electro DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ được tăng {1} Electro DMG.
+          <t>Biến thành Vitreum Dancer và tấn công kẻ địch xung quanh, gây {0} DMG Electro.
+Resonator trang bị Echo này ở vị trí chính sẽ được tăng {1} DMG Electro.
 Hồi chiêu: {2} giây.</t>
         </is>
       </c>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Biến thành Vitreum Dancer và gây Electro DMG lên kẻ địch. Gắn Echo này vào vị trí chính sẽ tăng thêm Electro DMG.</t>
+          <t>Biến hình thành Vitreum Dancer và gây Sát Thương Electro lên kẻ địch. Gắn Echo này vào vị trí chính sẽ tăng thêm Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Biến thành Cuddle Wuddle và tấn công kẻ địch bằng 4 đòn gây {0} Sát Thương Physical và 1 đòn gây {1} Sát Thương Physical.
+          <t>Biến hình thành Cuddle Wuddle và tấn công kẻ địch bằng 4 đòn gây {0} Sát Thương Vật Lý và 1 đòn gây {1} Sát Thương Vật Lý.
 Hồi chiêu: {2}s.</t>
         </is>
       </c>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Biến thành Cuddle Wuddle và liên tục gây Sát Thương Physical lên kẻ địch.</t>
+          <t>Biến hình thành Cuddle Wuddle và liên tục gây Sát Thương Vật Lý lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Summon một Chop Chop: Leftless tấn công kẻ địch, gây {0} Spectro DMG.
+          <t>Triệu hồi một Chop Chop: Leftless tấn công kẻ địch, gây {0} DMG Spectro.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Summon một Chop Chop: Leftless gây Spectro DMG cho kẻ địch.</t>
+          <t>Triệu hồi một Chop Chop: Leftless to deal Spectro DMG to enemies.</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Summon một Chop Chop: Rightless tấn công kẻ địch, gây {0} Havoc DMG.
+          <t>Triệu hồi một Chop Chop: Rightless tấn công kẻ địch, gây {0} DMG Havoc.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Summon một Chop Chop: Rightless gây Havoc DMG cho kẻ địch.</t>
+          <t>Triệu hồi một Chop Chop: Rightless to deal Havoc DMG to enemies.</t>
         </is>
       </c>
     </row>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Summon một Chop Chop: Headless tấn công kẻ địch, gây {0} Fusion DMG.
+          <t>Triệu hồi một Chop Chop: Headless tấn công kẻ địch, gây {0} DMG Fusion.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Summon một Chop Chop: Headless gây Fusion DMG cho kẻ địch.</t>
+          <t>Triệu hồi một Chop Chop: Headless to deal Fusion DMG to enemies.</t>
         </is>
       </c>
     </row>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Summon Fae Ignis tấn công kẻ địch, gây {0} Sát Thương Hỗn Loạn.
+          <t>Triệu hồi Fae Ignis tấn công kẻ địch, gây {0} Sát Thương Hỗn Loạn.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Summon Fae Ignis gây Sát Thương Hỗn Loạn lên kẻ địch.</t>
+          <t>Triệu hồi Fae Ignis gây Sát Thương Hỗn Loạn lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Summon Hồn Mây Nimbus hồi phục HP cho Resonator đang hoạt động bằng {0} HP tối đa của họ, tối đa 4 lần.
+          <t>Triệu hồi Hồn Mây Nimbus hồi phục HP cho Resonator đang hoạt động bằng {0} HP tối đa của họ, tối đa 4 lần.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Summon một Hocus Pocus tấn công kẻ địch bằng 3 đòn liên tiếp, mỗi đòn gây {0} Havoc DMG.
+          <t>Triệu hồi một Hocus Pocus tấn công kẻ địch bằng 3 đòn liên tiếp, mỗi đòn gây {0} Sát Thương Havoc.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Summon một Hocus Pocus gây Havoc DMG liên tiếp lên kẻ địch.</t>
+          <t>Triệu hồi một Hocus Pocus gây Sát Thương Havoc liên tiếp lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Summon Lottie Lost tấn công kẻ địch, gây {0} Spectro DMG.
+          <t>Triệu hồi Lottie Lost tấn công kẻ địch, gây {0} DMG Spectro.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Summon Lottie Lost gây Spectro DMG lên kẻ địch.</t>
+          <t>Triệu hồi Lottie Lost gây DMG Spectro lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Biến thành Diggy Duggy, bật lên không trung rồi đập xuống kẻ địch, gây {0} Sát Thương Physical.
+          <t>Biến hình thành Diggy Duggy, bật lên không trung rồi đập xuống kẻ địch, gây {0} Sát Thương Vật Lý.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Biến thành Diggy Duggy và gây Sát Thương Physical lên kẻ địch.</t>
+          <t>Biến hình thành Diggy Duggy và gây Sát Thương Vật Lý lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Summon Frostscourge Stalker tấn công kẻ địch, gây {0} Glacio DMG.
+          <t>Triệu hồi Frostscourge Stalker tấn công kẻ địch, gây {0} Sát Thương Glacio.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Summon Frostscourge Stalker gây Glacio DMG lên kẻ địch.</t>
+          <t>Triệu hồi Frostscourge Stalker gây Sát Thương Glacio lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Summon Kẻ Rình Rập Voltscourge thực hiện 3 đợt tấn công, mỗi đợt gây {0} Electro DMG.
+          <t>Triệu hồi Kẻ Rình Rập Voltscourge thực hiện 3 đợt tấn công, mỗi đợt gây {0} Sát Thương Electro.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Summon Kẻ Rình Rập Voltscourge tấn công kẻ địch bằng Electro DMG.</t>
+          <t>Triệu hồi Kẻ Rình Rập Voltscourge tấn công kẻ địch bằng Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Summon Galescourge Stalker hồi phục HP cho các Resonator gần đó {0} HP tối đa, tối đa 3 lần.
+          <t>Triệu hồi Galescourge Stalker hồi phục HP cho các Cộng Hưởng Giả gần đó {0} HP tối đa, tối đa 3 lần.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Summon một Chest Mimic tấn công kẻ địch bằng 3 đòn liên tiếp, mỗi đòn gây {0} Spectro DMG.
+          <t>Triệu hồi một Chest Mimic tấn công kẻ địch bằng 3 đòn liên tiếp, mỗi đòn gây {0} Sát Thương Spectro.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Summon một Chest Mimic gây Spectro DMG liên tiếp lên kẻ địch.</t>
+          <t>Triệu hồi một Chest Mimic gây Sát Thương Spectro liên tiếp lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Summon Golden Junrock lao về phía trước, gây {0} Spectro DMG cho kẻ địch trên đường đi.
+          <t>Triệu hồi Golden Junrock lao về phía trước, gây {0} Sát Thương Spectro cho kẻ địch trên đường đi.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Summon Golden Junrock gây Spectro DMG cho kẻ địch.</t>
+          <t>Triệu hồi Golden Junrock gây Sát Thương Spectro cho kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -10581,7 +10581,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Summon một Calcified Junrock để hồi HP cho Resonators gần đó trong đội bằng {0} HP tối đa của họ, tối đa 5 lần.
+          <t>Triệu hồi một Calcified Junrock để hồi HP cho các Resonator gần đó trong đội bằng {0} HP tối đa của họ, tối đa 5 lần.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -10648,7 +10648,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Summon Aero Prism tấn công kẻ địch, gây {0} Sát Thương Gió.
+          <t>Triệu hồi Lăng Kính Gió tấn công kẻ địch, gây {0} Sát Thương Gió.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Summon Aero Prism gây Sát Thương Gió lên kẻ địch.</t>
+          <t>Triệu hồi Lăng Kính Gió gây Sát Thương Gió lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Biến thành Nổi Giận Trước Tượng Đài để tấn công kẻ địch, gây {0} Spectro DMG. Giữ Kỹ Năng Echo để duy trì hình dạng Echo và lao về phía kẻ địch, gây {1} Spectro DMG.
+          <t>Biến hình thành Nổi Giận Trước Tượng Đài để tấn công kẻ địch, gây {0} Sát Thương Spectro. Giữ Kỹ Năng Echo để duy trì hình dạng Echo và lao về phía kẻ địch, gây {1} Sát Thương Spectro.
 Hồi chiêu: {2} giây.</t>
         </is>
       </c>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Biến thành Nổi Giận Trước Tượng Đài và gây Spectro DMG lên kẻ địch. Giữ Kỹ Năng Echo để lao về phía kẻ địch, gây Spectro DMG.</t>
+          <t>Biến hình thành Nổi Giận Trước Tượng Đài và gây Sát Thương Spectro lên kẻ địch. Giữ Kỹ Năng Echo để lao về phía kẻ địch, gây Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -10912,7 +10912,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Biến thành Hurriclaw và lao về phía trước, gây {0} Sát Thương Hệ Aero khi trúng mục tiêu, cộng thêm {1} Sát Thương Hệ Aero với đòn quét. Giữ Kỹ Năng Echo để tiếp tục lao về phía trước. Dùng lại Kỹ Năng Echo trong khi lao để thực hiện đòn quét.
+          <t>Biến hình thành Hurriclaw và lao về phía trước, gây {0} Sát Thương Hệ Aero khi trúng mục tiêu, cộng thêm {1} Sát Thương Hệ Aero với đòn quét. Giữ Kỹ Năng Echo để tiếp tục lao về phía trước. Dùng lại Kỹ Năng Echo trong khi lao để thực hiện đòn quét.
 Hồi chiêu: {2} giây.</t>
         </is>
       </c>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Biến thành Hurriclaw và lao về phía trước, gây Sát Thương Hệ Aero lên kẻ địch.</t>
+          <t>Biến hình thành Hurriclaw và lao về phía trước, gây Sát Thương Hệ Aero lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -11045,8 +11045,8 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Biến thành La Guardia và tấn công các mục tiêu gần đó, gây {0} Sát Thương Physical.
-Giữ Kỹ Năng Echo để duy trì dạng Echo trong một khoảng thời gian, chém kẻ địch và bắn một đòn tấn công tầm xa về phía trước. Đòn chém gây {1} Sát Thương Physical, và đòn tấn công tầm xa gây {3} Sát Thương Physical tối đa {2} lần.
+          <t>Biến hình thành La Guardia và tấn công các mục tiêu gần đó, gây {0} Sát Thương Vật Lý.
+Giữ Kỹ Năng Echo để duy trì dạng Echo trong một khoảng thời gian, chém kẻ địch và bắn một đòn tấn công tầm xa về phía trước. Đòn chém gây {1} Sát Thương Vật Lý, và đòn tấn công tầm xa gây {3} Sát Thương Vật Lý tối đa {2} lần.
 Hồi chiêu: {4} giây.</t>
         </is>
       </c>
@@ -11112,7 +11112,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Biến thành La Guardia và gây Sát Thương Physical lên kẻ địch. Giữ Kỹ Năng Vang Âm để phóng đòn tấn công tầm xa gây Sát Thương Physical.</t>
+          <t>Biến hình thành La Guardia và gây Sát Thương Vật Lý lên kẻ địch. Giữ Kỹ Năng Vang Âm để phóng đòn tấn công tầm xa gây Sát Thương Vật Lý.</t>
         </is>
       </c>
     </row>
@@ -11179,8 +11179,8 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Biến thành Sagittario để di chuyển một khoảng cách nhất định và thực hiện đòn tấn công tầm xa, gây {0} Spectro DMG.
-Bị tấn công trong khi di chuyển ở dạng Sagittario sẽ kích hoạt Dodge Counter tăng cường, tránh sát thương và gây {1} Spectro DMG một lần và {2} Spectro DMG 5 lần.
+          <t>Biến hình thành Sagittario để di chuyển một khoảng cách nhất định và thực hiện đòn tấn công tầm xa, gây {0} Sát Thương Spectro.
+Bị tấn công trong khi di chuyển ở dạng Sagittario sẽ kích hoạt Dodge Counter tránh tăng cường, tránh DMG và gây {1} Sát Thương Spectro một lần và {2} Sát Thương Spectro 5 lần.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Biến thành Sagittario để di chuyển và gây Spectro DMG cho kẻ địch. Bị tấn công trong khi di chuyển ở dạng Sagittario sẽ kích hoạt Dodge Counter tăng cường, tránh sát thương.</t>
+          <t>Biến hình thành Sagittario để di chuyển và gây Sát Thương Spectro cho kẻ địch. Bị tấn công trong khi di chuyển ở dạng Sagittario sẽ kích hoạt Dodge Counter tránh tăng cường, tránh DMG.</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11312,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Summon Sacerdos tấn công kẻ địch, gây {0} Aero DMG 2 lần.
+          <t>Triệu hồi Sacerdos tấn công kẻ địch, gây {0} Sát Thương Aero 2 lần.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Summon Sacerdos gây Aero DMG lên kẻ địch.</t>
+          <t>Triệu hồi Sacerdos gây Sát Thương Aero lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Summon một Aero Drake tấn công kẻ địch, gây {0} Aero DMG.
+          <t>Triệu hồi một Aero Drake tấn công kẻ địch, gây {0} Sát Thương Aero.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Summon một Aero Drake gây Aero DMG lên kẻ địch.</t>
+          <t>Triệu hồi một Aero Drake gây Sát Thương Aero lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Summon Rồng Sét tấn công kẻ địch, gây {0} Sát Thương Sét 3 lần.
+          <t>Triệu hồi Rồng Sét tấn công kẻ địch, gây {0} Sát Thương Sét 3 lần.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Summon Rồng Sét gây Sát Thương Sét lên kẻ địch.</t>
+          <t>Triệu hồi Rồng Sét gây Sát Thương Sét lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Summon Glacio Drake tấn công kẻ địch, gây {0} Glacio DMG 5 lần.
+          <t>Triệu hồi Glacio Drake tấn công kẻ địch, gây {0} Sát Thương Glacio 5 lần.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Summon Glacio Drake gây Glacio DMG lên kẻ địch.</t>
+          <t>Triệu hồi Glacio Drake gây Sát Thương Glacio lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -11841,8 +11841,8 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Summon một Capitaneus nhảy lên và đập mạnh kẻ địch, gây {0} Spectro DMG. Đòn tấn công này tạo thêm 4 Merciless Judgement, mỗi đòn gây {1} Spectro DMG.
-Resonator gắn Echo này vào vị trí chính sẽ nhận được {2} Spectro DMG Bonus và {3} Tăng Sát Thương Heavy Attack.
+          <t>Triệu hồi một Capitaneus nhảy lên và đập mạnh kẻ địch, gây {0} Sát Thương Spectro. Đòn tấn công này tạo thêm 4 Merciless Judgement, mỗi đòn gây {1} Sát Thương Spectro.
+Resonator gắn Echo này vào vị trí chính sẽ nhận được {2} Tăng Sát Thương Spectro và {3} Tăng Sát Thương Đòn Nặng.
 Hồi chiêu: {4} giây.</t>
         </is>
       </c>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Summon một Capitaneus và gây Spectro DMG lên kẻ địch. Gắn Echo này vào vị trí chính sẽ tăng Spectro DMG và Sát Thương Heavy Attack.</t>
+          <t>Triệu hồi một Capitaneus và gây Sát Thương Spectro lên kẻ địch. Gắn Echo này vào vị trí chính sẽ tăng Sát Thương Spectro và Sát Thương Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -11974,7 +11974,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Summon Fusion Drake tấn công kẻ địch 3 lần, mỗi lần gây {0} Fusion DMG.
+          <t>Triệu hồi Fusion Drake tấn công kẻ địch 3 lần, mỗi lần gây {0} Sát Thương Fusion.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -12040,7 +12040,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Summon Fusion Drake gây Fusion DMG lên kẻ địch.</t>
+          <t>Triệu hồi Fusion Drake gây Sát Thương Fusion lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -12106,7 +12106,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Summon Spectro Drake tấn công kẻ địch, gây {0} Spectro DMG 3 lần.
+          <t>Triệu hồi Spectro Drake tấn công kẻ địch, gây {0} Sát Thương Spectro 3 lần.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Summon Drake Ngân Hưởng gây Sát Thương Ngân Hưởng lên kẻ địch.</t>
+          <t>Triệu hồi Drake Ngân Hưởng gây Sát Thương Ngân Hưởng lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Summon một Havoc Drake tấn công kẻ địch, gây {0} Havoc DMG 3 lần.
+          <t>Triệu hồi một Havoc Drake tấn công kẻ địch, gây {0} Sát Thương Havoc 3 lần.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -12304,7 +12304,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Summon một Havoc Drake gây Havoc DMG lên kẻ địch.</t>
+          <t>Triệu hồi một Havoc Drake gây Sát Thương Havoc lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Summon Devotee's Flesh tấn công kẻ địch, gây {0} Sát Thương Gió 3 lần.
+          <t>Triệu hồi Thịt Tín Đồ tấn công kẻ địch, gây {0} Sát Thương Gió 3 lần.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Summon Devotee's Flesh gây Sát Thương Gió lên kẻ địch.</t>
+          <t>Triệu hồi Thịt Tín Đồ gây Sát Thương Gió lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Biến thành Pilgrim's Shell để tấn công kẻ địch xung quanh, gây {0} Aero DMG.
+          <t>Biến hình thành Pilgrim's Shell để tấn công kẻ địch xung quanh, gây {0} Sát Thương Aero.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Biến thành Pilgrim's Shell để tấn công kẻ địch xung quanh, gây Aero DMG.</t>
+          <t>Biến hình thành Pilgrim's Shell để tấn công kẻ địch xung quanh, gây Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Biến thành Kerasaur, nhảy lên không trung và đập xuống, gây {0} Sát Thương Hệ Aero. Ngay sau khi trúng mục tiêu, dùng lại Kỹ Năng Echo để lao vào mục tiêu, gây {1} Sát Thương Hệ Aero.
+          <t>Biến hình thành Kerasaur, nhảy lên không trung và đập xuống, gây {0} Sát Thương Hệ Aero. Ngay sau khi trúng mục tiêu, dùng lại Kỹ Năng Echo để lao vào mục tiêu, gây {1} Sát Thương Hệ Aero.
 Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {2} Tăng Sát Thương Hệ Aero và {3} Tăng Sát Thương Kỹ Năng Resonance Liberation.
 Hồi chiêu: {4} giây</t>
         </is>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Biến thành Kerasaur, nhảy lên không trung và đập xuống, gây Sát Thương Hệ Aero. Ngay sau khi trúng mục tiêu, dùng lại Kỹ Năng Echo để lao vào mục tiêu, gây Sát Thương Hệ Aero.
+          <t>Biến hình thành Kerasaur, nhảy lên không trung và đập xuống, gây Sát Thương Hệ Aero. Ngay sau khi trúng mục tiêu, dùng lại Kỹ Năng Echo để lao vào mục tiêu, gây Sát Thương Hệ Aero.
 Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm Tăng Sát Thương Hệ Aero và Tăng Sát Thương Kỹ Năng Resonance Liberation.</t>
         </is>
       </c>
@@ -12771,8 +12771,8 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Biến thành Thundering Mephis, tung ra loạt tấn công nhanh gồm tối đa 6 đòn. Năm đòn đầu gây {0} Electro DMG mỗi đòn, đòn cuối gây {1} Electro DMG, cộng thêm {2} Electro DMG từ sét.
-Sau đòn cuối, tăng Electro DMG của nhân vật hiện tại {3} và sát thương Resonance Liberation {4} trong {5} giây.
+          <t>Biến thành Thundering Mephis, tung ra loạt tấn công nhanh gồm tối đa 6 đòn. Năm đòn đầu gây {0} DMG Electro mỗi đòn, đòn cuối gây {1} DMG Electro, cộng thêm {2} DMG Electro từ sét.
+Sau đòn cuối, tăng DMG Electro của nhân vật hiện tại {3} và DMG Resonance Liberation {4} trong {5} giây.
 Hồi chiêu: {6} giây.</t>
         </is>
       </c>
@@ -12838,7 +12838,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Biến thành Thundering Mephis để gây Electro DMG. Increase Electro DMG và sát thương Resonance Liberation của nhân vật hiện tại.</t>
+          <t>Biến thành Thundering Mephis để gây DMG Electro. Tăng DMG Electro và DMG Resonance Liberation của nhân vật hiện tại.</t>
         </is>
       </c>
     </row>
@@ -12906,9 +12906,9 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Biến thành Inferno Rider để tung ra tối đa 3 nhát chém liên tiếp, mỗi nhát gây {0}, {1} và {2} Fusion DMG tương ứng.
-Sau đòn cuối, tăng Fusion DMG của Resonator hiện tại lên {3} và Sát Thương Basic Attack lên {4} trong {5} giây.
-Giữ lâu Kỹ Năng Echo để biến hình thành Inferno Rider và vào Chế Độ Cưỡi. Khi thoát Chế Độ Cưỡi, gây {2} Fusion DMG lên kẻ địch phía trước.
+          <t>Biến hình thành Kỵ Sĩ Hỏa Ngục để tung ra tối đa 3 nhát chém liên tiếp, mỗi nhát gây {0}, {1} và {2} Sát Thương Fusion tương ứng.
+Sau đòn cuối, tăng Sát Thương Fusion của Resonator hiện tại lên {3} và Sát Thương Basic Attack lên {4} trong {5} giây.
+Giữ lâu Kỹ Năng Echo để biến hình thành Kỵ Sĩ Hỏa Ngục và vào Chế Độ Cưỡi. Khi thoát Chế Độ Cưỡi, gây {2} Sát Thương Fusion lên kẻ địch phía trước.
 Hồi chiêu: {6} giây</t>
         </is>
       </c>
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Biến thành Inferno Rider để thực hiện các đòn tấn công liên tiếp, gây Fusion DMG và tăng Fusion DMG cùng Sát Thương Basic Attack. Giữ Kỹ Năng Echo để vào Chế Độ Cưỡi.</t>
+          <t>Biến hình thành Kỵ Sĩ Hỏa Ngục để thực hiện các đòn tấn công liên tiếp, gây Sát Thương Fusion và tăng Sát Thương Fusion cùng Sát Thương Basic Attack. Giữ Kỹ Năng Echo để vào Chế Độ Cưỡi.</t>
         </is>
       </c>
     </row>
@@ -13041,8 +13041,8 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Triệu hồi sự bảo hộ của Rùa Địa Hình Chuông Bảo Hộ. Gây Glacio DMG dựa trên {0} DEF của nhân vật hiện tại lên kẻ địch xung quanh, và nhận Shield Chuông Bảo Hộ kéo dài {1} giây
-Shield Chuông Bảo Hộ cung cấp {2} Giảm Sát Thương và {3} Tăng Sát Thương cho các thành viên trong đội hiện tại, và sẽ biến mất sau khi nhân vật hiện tại bị tấn công {4} lần.
+          <t>Triệu hồi sự bảo hộ của Rùa Địa Hình Chuông Bảo Hộ. Gây Sát Thương Glacio dựa trên {0} DEF của nhân vật hiện tại lên kẻ địch xung quanh, và nhận Khiên Chuông Bảo Hộ kéo dài {1} giây
+Khiên Chuông Bảo Hộ cung cấp {2} Giảm Sát Thương và {3} Tăng Sát Thương cho các thành viên trong đội hiện tại, và sẽ biến mất sau khi nhân vật hiện tại bị tấn công {4} lần.
 Hồi chiêu: {5} giây</t>
         </is>
       </c>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Triệu hồi Rùa Địa Hình Chuông Bảo Hộ, gây Glacio DMG lên kẻ địch xung quanh dựa trên DEF của nhân vật hiện tại. Giảm sát thương nhận vào, tăng sát thương gây ra.</t>
+          <t>Triệu hồi Rùa Địa Hình Chuông Bảo Hộ, gây Sát Thương Glacio lên kẻ địch xung quanh dựa trên DEF của nhân vật hiện tại. Giảm DMG nhận vào, tăng DMG gây ra.</t>
         </is>
       </c>
     </row>
@@ -13175,8 +13175,8 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Biến thành Tempest Mephis để thực hiện đòn quất đuôi liên tiếp rồi kết thúc bằng đòn cào. Đòn sét từ cú quất đuôi gây {0} Electro DMG mỗi lần, còn đòn cào gây {1} Electro DMG.
-Sau khi đòn cào trúng mục tiêu, tăng Electro DMG của nhân vật hiện tại {2} và sát thương Heavy Attack {3} trong {4} giây.
+          <t>Biến thành Tempest Mephis để thực hiện đòn quất đuôi liên tiếp rồi kết thúc bằng đòn cào. Đòn sét từ cú quất đuôi gây {0} DMG Electro mỗi lần, còn đòn cào gây {1} DMG Electro.
+Sau khi đòn cào trúng mục tiêu, tăng DMG Electro của nhân vật hiện tại {2} và DMG Đòn Nặng {3} trong {4} giây.
 Hồi chiêu: {5} giây.</t>
         </is>
       </c>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Biến thành Tempest Mephis để tấn công liên tục kẻ địch, gây Electro DMG. Increase Electro DMG và sát thương Heavy Attack của nhân vật hiện tại.</t>
+          <t>Biến thành Tempest Mephis để tấn công liên tục kẻ địch, gây DMG Electro. Tăng DMG Electro và DMG Đòn Nặng của nhân vật hiện tại.</t>
         </is>
       </c>
     </row>
@@ -13309,8 +13309,8 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Biến thành Crownless và thực hiện tối đa 4 đòn tấn công liên tiếp. Hai đòn đầu gây {0} Havoc DMG mỗi đòn, đòn thứ ba gây {1} Havoc DMG 2 lần, và đòn thứ tư gây {2} Havoc DMG 3 lần.
-Sau khi biến hình, tăng Havoc DMG của nhân vật hiện tại lên {3} và Sát Thương Resonance Skill lên {4} trong {5}s.
+          <t>Biến hình thành Crownless và thực hiện tối đa 4 đòn tấn công liên tiếp. Hai đòn đầu gây {0} Sát Thương Havoc mỗi đòn, đòn thứ ba gây {1} Sát Thương Havoc 2 lần, và đòn thứ tư gây {2} Sát Thương Havoc 3 lần.
+Sau khi biến hình, tăng Sát Thương Havoc của nhân vật hiện tại lên {3} và Sát Thương Resonance Skill lên {4} trong {5}s.
 Hồi chiêu: {6}s</t>
         </is>
       </c>
@@ -13376,7 +13376,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Biến thành Crownless và tấn công kẻ địch không ngừng nghỉ, gây Havoc DMG. Increase Havoc DMG và Sát Thương Resonance Skill của nhân vật hiện tại.</t>
+          <t>Biến hình thành Crownless và tấn công kẻ địch không ngừng nghỉ, gây Sát Thương Havoc. Tăng Sát Thương Havoc và Sát Thương Resonance Skill của nhân vật hiện tại.</t>
         </is>
       </c>
     </row>
@@ -13443,8 +13443,8 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Biến thành Feilian Beringal và tung cú đá mạnh. Nếu cú đá trúng kẻ địch, lập tức thực hiện đòn tấn công tiếp theo. Cú đá gây {0} Aero DMG, đòn tiếp theo gây {1} Aero DMG.
-Sau khi đòn tiếp theo trúng mục tiêu, Aero DMG của nhân vật hiện tại tăng {2} và Sát Thương Heavy Attack tăng {3} trong {4} giây.
+          <t>Biến hình thành Feilian Beringal và tung cú đá mạnh. Nếu cú đá trúng kẻ địch, lập tức thực hiện đòn tấn công tiếp theo. Cú đá gây {0} Sát Thương Aero, đòn tiếp theo gây {1} Sát Thương Aero.
+Sau khi đòn tiếp theo trúng mục tiêu, Sát Thương Aero của nhân vật hiện tại tăng {2} và Sát Thương Đòn Nặng tăng {3} trong {4} giây.
 Hồi chiêu: {5} giây</t>
         </is>
       </c>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Biến thành Feilian Beringal để liên tục tấn công kẻ địch, gây Aero DMG. Increase Aero DMG và Sát Thương Heavy Attack của nhân vật hiện tại.</t>
+          <t>Biến hình thành Feilian Beringal để liên tục tấn công kẻ địch, gây Sát Thương Aero. Tăng Sát Thương Aero và Sát Thương Đòn Nặng của nhân vật hiện tại.</t>
         </is>
       </c>
     </row>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Biến thành Lampylumen Myriad. Thực hiện tối đa 3 đòn tấn công liên tiếp.
+          <t>Biến hình thành Lampylumen Myriad. Thực hiện tối đa 3 đòn tấn công liên tiếp.
 Phóng một cú sốc đóng băng bằng các đòn đánh về phía trước, hai đòn đầu gây {0} và {1} Sát Thương Băng, đòn cuối gây {2} Sát Thương Băng. Kẻ địch trúng đòn sẽ bị đóng băng.
 Mỗi cú sốc tăng Sát Thương Băng của nhân vật hiện tại lên {3} và Sát Thương Resonance Skill lên {4} trong {5} giây, tối đa 3 lần cộng dồn.
 Hồi chiêu: {6} giây.</t>
@@ -13646,7 +13646,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Biến thành Lampylumen Myriad để tấn công liên tục kẻ địch, gây Sát Thương Băng. Increase Sát Thương Băng và Sát Thương Resonance Skill của nhân vật hiện tại.</t>
+          <t>Biến hình thành Lampylumen Myriad để tấn công liên tục kẻ địch, gây Sát Thương Băng. Tăng Sát Thương Băng và Sát Thương Resonance Skill của nhân vật hiện tại.</t>
         </is>
       </c>
     </row>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Biến thành Mourning Aix và thực hiện 2 đòn cào liên tiếp, mỗi đòn gây {0} và {1} Sát Thương Dị Giới tương ứng.
+          <t>Biến hình thành Mourning Aix và thực hiện 2 đòn cào liên tiếp, mỗi đòn gây {0} và {1} Sát Thương Dị Giới tương ứng.
 Sau khi biến hình, tăng Sát Thương Dị Giới của nhân vật hiện tại lên {2} và Sát Thương Resonance Liberation lên {3} trong {4} giây.
 Hồi chiêu: {5} giây.</t>
         </is>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Biến thành Mourning Aix để tấn công liên tục kẻ địch, gây Sát Thương Dị Giới. Increase Sát Thương Dị Giới và Sát Thương Resonance Liberation của nhân vật hiện tại.</t>
+          <t>Biến hình thành Mourning Aix để tấn công liên tục kẻ địch, gây Sát Thương Dị Giới. Tăng Sát Thương Dị Giới và Sát Thương Resonance Liberation của nhân vật hiện tại.</t>
         </is>
       </c>
     </row>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Gây Electro DMG lên kẻ địch xung quanh và tạo ra Mech Waste phát nổ sau một lúc. Increase Tấn Công cho người sử dụng.</t>
+          <t>Gây Sát Thương Electro lên kẻ địch xung quanh và tạo ra Mech Waste phát nổ sau một lúc. Tăng ATK cho người sử dụng.</t>
         </is>
       </c>
     </row>
@@ -13913,9 +13913,9 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Biến thành Impermanence Heron, bay lên và đập xuống, gây {0} Sát Thương Hệ Havoc.
+          <t>Biến hình thành Impermanence Heron, bay lên và đập xuống, gây {0} Sát Thương Hệ Havoc.
 Giữ lâu để duy trì dạng Impermanence Heron và liên tục phun lửa, mỗi đòn gây {1} Sát Thương Hệ Havoc.
-Khi đòn tấn công đầu tiên trúng kẻ địch, nhân vật hiện tại sẽ hồi phục 10 Resonance Energy. Nếu nhân vật hiện tại sử dụng Outro Skill trong vòng 15 giây tiếp theo, sát thương của nhân vật kế tiếp sẽ được tăng 12% trong 15 giây.
+Khi đòn tấn công đầu tiên trúng kẻ địch, nhân vật hiện tại sẽ hồi phục 10 Resonance Energy. Nếu nhân vật hiện tại sử dụng Kỹ Năng Outro trong vòng 15 giây tiếp theo, DMG của nhân vật kế tiếp sẽ được tăng 12% trong 15 giây.
 Hồi chiêu: {2} giây</t>
         </is>
       </c>
@@ -13981,7 +13981,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Biến thành Impermanence Heron để gây Sát Thương Hệ Havoc. Giữ lâu để phun lửa và liên tục gây Sát Thương Hệ Havoc. Khi tấn công trúng bất kỳ kẻ địch nào, hồi phục Resonance Energy cho nhân vật hiện tại. Increase sát thương của nhân vật tiếp theo.</t>
+          <t>Biến hình thành Impermanence Heron để gây Sát Thương Hệ Havoc. Giữ lâu để phun lửa và liên tục gây Sát Thương Hệ Havoc. Khi tấn công trúng bất kỳ kẻ địch nào, hồi phục Resonance Energy cho nhân vật hiện tại. Tăng DMG của nhân vật tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -14048,8 +14048,8 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Biến thành Dreamless, thực hiện 6 đòn tấn công liên tiếp. Năm đòn đầu gây {0} Havoc DMG mỗi đòn, đòn cuối gây {1} Havoc DMG.
-Sát thương của Kỹ Năng Echo này tăng thêm {3} trong {2} giây đầu sau khi Rover: Havoc sử dụng Resonance Liberation: Vực Hư Vô.
+          <t>Biến hình thành Dreamless, thực hiện 6 đòn tấn công liên tiếp. Năm đòn đầu gây {0} Sát Thương Havoc mỗi đòn, đòn cuối gây {1} Sát Thương Havoc.
+DMG của Kỹ Năng Echo này tăng thêm {3} trong {2} giây đầu sau khi Rover: Havoc sử dụng Resonance Liberation: Vực Hư Vô.
 Hồi chiêu: {4} giây.</t>
         </is>
       </c>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Biến thành Dreamless để liên tục tấn công kẻ địch, gây Havoc DMG. Kỹ Năng Echo này gây sát thương cao hơn sau khi Rover-Havoc sử dụng Resonance Liberation của mình.</t>
+          <t>Biến hình thành Dreamless để liên tục tấn công kẻ địch, gây Sát Thương Havoc. Kỹ Năng Echo này gây DMG cao hơn sau khi Rover-Havoc sử dụng Resonance Liberation của mình.</t>
         </is>
       </c>
     </row>
@@ -14184,10 +14184,10 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Summon Jué trợ chiến. Jué bay lượn trên không, gây {0} Spectro DMG và triệu hồi sấm sét giáng xuống kẻ địch gần đó tối đa 5 lần, mỗi lần gây {1} Spectro DMG. Sau đó, Jué xoáy xuống tấn công kẻ địch xung quanh hai lần, mỗi lần gây {2} Spectro DMG.
-Sử dụng Kỹ Năng Echo này sẽ ban cho Resonator hiệu ứng Blessing Thời Gian kéo dài {3} giây, trong đó:
+          <t>Triệu hồi Jué trợ chiến. Jué bay lượn trên không, gây {0} Sát Thương Spectro và triệu hồi sấm sét giáng xuống kẻ địch gần đó tối đa 5 lần, mỗi lần gây {1} Sát Thương Spectro. Sau đó, Jué xoáy xuống tấn công kẻ địch xung quanh hai lần, mỗi lần gây {2} Sát Thương Spectro.
+Sử dụng Kỹ Năng Echo này sẽ ban cho Resonator hiệu ứng Phước Lành Thời Gian kéo dài {3} giây, trong đó:
 - Resonator nhận thêm {4} Tăng Sát Thương Kỹ Năng Echo.
-- Khi Kỹ Năng Echo của Resonator trúng mục tiêu, gây {5} Spectro DMG mỗi giây trong {6} giây, được tính là Sát Thương Kỹ Năng Echo của Resonator.
+- Khi Kỹ Năng Echo của Resonator trúng mục tiêu, gây {5} Sát Thương Spectro mỗi giây trong {6} giây, được tính là Sát Thương Kỹ Năng Echo của Resonator.
 Hồi chiêu: {7} giây.</t>
         </is>
       </c>
@@ -14253,7 +14253,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Summon Jué tấn công kẻ địch, gây Spectro DMG. Resonator có thể sử dụng Resonance Skill để gây Spectro DMG liên tục theo thời gian.</t>
+          <t>Triệu hồi Jué tấn công kẻ địch, gây DMG Spectro. Resonator có thể sử dụng Resonance Skill để gây DMG Spectro liên tục theo thời gian.</t>
         </is>
       </c>
     </row>
@@ -14321,9 +14321,9 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Biến thành Sentry Construct và tấn công kẻ địch phía trước, gây {0} Glacio DMG. Mỗi lần Resonator sở hữu Echo này sử dụng Resonance Liberation, nó sẽ nạp cho Strike Capacitor.
-Khi Strike Capacitor đạt cấp tối đa, Cooldown của Kỹ Năng Echo sẽ được đặt lại. Sử dụng Kỹ Năng Echo để biến hình thành Sentry Construct và lao từ trên không xuống kẻ địch, gây {1} Glacio DMG và đóng băng mục tiêu.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận được {2} Glacio DMG Bonus và {3} Tăng Sát Thương Resonance Skill.
+          <t>Biến hình thành Sentry Construct và tấn công kẻ địch phía trước, gây {0} Sát Thương Glacio. Mỗi lần Resonator sở hữu Echo này sử dụng Resonance Liberation, nó sẽ nạp cho Strike Capacitor.
+Khi Strike Capacitor đạt cấp tối đa, hồi chiêu của Kỹ Năng Echo sẽ được đặt lại. Sử dụng Kỹ Năng Echo để biến hình thành Sentry Construct và lao từ trên không xuống kẻ địch, gây {1} Sát Thương Glacio và đóng băng mục tiêu.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận được {2} Tăng Sát Thương Glacio và {3} Tăng Sát Thương Resonance Skill.
 Hồi chiêu: {4} giây.</t>
         </is>
       </c>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Biến thành Sentry Construct và gây Glacio DMG cho kẻ địch. Sử dụng Resonance Liberation khi trang bị Echo này sẽ tăng cường Strike Capacitor. Khi Strike Capacitor đạt tối đa, biến hình thành Sentry Construct và gây Glacio DMG cho kẻ địch. Trang bị Echo này ở vị trí chính sẽ nhận được Glacio DMG Bonus và Tăng Sát Thương Resonance Skill.</t>
+          <t>Biến hình thành Sentry Construct và gây Sát Thương Glacio cho kẻ địch. Sử dụng Resonance Liberation khi trang bị Echo này sẽ tăng cường Strike Capacitor. Khi Strike Capacitor đạt tối đa, biến hình thành Sentry Construct và gây Sát Thương Glacio cho kẻ địch. Trang bị Echo này ở vị trí chính sẽ nhận được Tăng Sát Thương Glacio và Tăng Sát Thương Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -14456,8 +14456,8 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Biến thành Dragon Than Khóc, triệu hồi Vực Sầu tồn tại trong 5 giây. Định kỳ gây {0} Fusion DMG lên kẻ địch trong phạm vi ảnh hưởng.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận được {1} Fusion DMG Bonus và {2} Tăng Sát Thương Basic Attack.
+          <t>Biến hình thành Rồng Than Khóc, triệu hồi Vực Sầu tồn tại trong 5 giây. Định kỳ gây {0} Sát Thương Fusion lên kẻ địch trong phạm vi ảnh hưởng.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận được {1} Tăng Sát Thương Fusion và {2} Tăng Sát Thương Basic Attack.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -14523,7 +14523,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Biến thành Dragon Than Khóc, triệu hồi Vực Sầu, gây Fusion DMG lên kẻ địch theo thời gian. Trang bị Echo này ở vị trí chính sẽ tăng Fusion DMG và Sát Thương Basic Attack.</t>
+          <t>Biến hình thành Rồng Than Khóc, triệu hồi Vực Sầu, gây Sát Thương Fusion lên kẻ địch theo thời gian. Trang bị Echo này ở vị trí chính sẽ tăng Sát Thương Fusion và Sát Thương Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -14590,8 +14590,8 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Summon 3 Crescent Servant xoay tròn quanh bạn. Crescent Servant tấn công kẻ địch bằng lưỡi kiếm xoay, gây {0} Havoc DMG. Kích hoạt Phản Công bằng Echo sẽ làm mới thời gian tồn tại của Crescent Servant.
-Resonator trang bị Echo này ở vị trí chính sẽ được tăng {1} Sát Thương Attack Phối Hợp.
+          <t>Triệu hồi 3 Crescent Servant xoay tròn quanh bạn. Crescent Servant tấn công kẻ địch bằng lưỡi kiếm xoay, gây {0} Sát Thương Havoc. Kích hoạt Phản Công bằng Echo sẽ làm mới thời gian tồn tại của Crescent Servant.
+Resonator trang bị Echo này ở vị trí chính sẽ được tăng {1} Sát Thương Tấn Công Phối Hợp.
 Hồi chiêu: {2} giây</t>
         </is>
       </c>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Summon Tôi Tớ Trăng Lưỡi Liềm để gây Sát Thương Hỗn Loạn lên kẻ địch. Khi phản công thành công bằng các đòn tấn công, thời gian triệu hồi sẽ được làm mới. Trang bị Echo này ở vị trí chính sẽ tăng Sát Thương Attack Phối Hợp.</t>
+          <t>Triệu hồi Tôi Tớ Trăng Lưỡi Liềm để gây Sát Thương Hỗn Loạn lên kẻ địch. Khi phản công thành công bằng các đòn tấn công, thời gian triệu hồi sẽ được làm mới. Trang bị Echo này ở vị trí chính sẽ tăng Sát Thương Tấn Công Phối Hợp.</t>
         </is>
       </c>
     </row>
@@ -14724,8 +14724,8 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Biến thành Lorelei và tấn công kẻ địch xung quanh, gây {0} Sát Thương Hỗn Loạn.
-Resonator trang bị Vang Âm này ở vị trí chính sẽ nhận {1} Tăng Sát Thương Hỗn Loạn và {2} Tăng Sát Thương Basic Attack.
+          <t>Biến hình thành Lorelei và tấn công kẻ địch xung quanh, gây {0} Sát Thương Hỗn Loạn.
+Resonator trang bị Vang Âm này ở vị trí chính sẽ nhận {1} Tăng Sát Thương Hỗn Loạn và {2} Tăng Sát Thương Đòn Cơ Bản.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Biến thành Lorelei và gây Sát Thương Hỗn Loạn lên kẻ địch. Trang bị Vang Âm này ở vị trí chính sẽ tăng Sát Thương Hỗn Loạn và Sát Thương Basic Attack.</t>
+          <t>Biến hình thành Lorelei và gây Sát Thương Hỗn Loạn lên kẻ địch. Trang bị Vang Âm này ở vị trí chính sẽ tăng Sát Thương Hỗn Loạn và Sát Thương Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -14858,8 +14858,8 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Summon Nightmare: Feilian Beringal tấn công kẻ địch, gây {0} Aero DMG. Tia Xoáy còn lại sẽ liên tục tấn công kẻ địch xung quanh tối đa 5 lần, mỗi lần gây {1} Aero DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {2} Aero DMG Bonus và {3} Tăng Sát Thương Heavy Attack.
+          <t>Triệu hồi Ác Mộng: Feilian Beringal tấn công kẻ địch, gây {0} DMG Aero. Tia Xoáy còn lại sẽ liên tục tấn công kẻ địch xung quanh tối đa 5 lần, mỗi lần gây {1} DMG Aero.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {2} Tăng Sát Thương Aero và {3} Tăng Sát Thương Đòn Nặng.
 Hồi chiêu: {4} giây.</t>
         </is>
       </c>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Summon Nightmare: Feilian Beringal gây Aero DMG lên kẻ địch. Tia Xoáy còn lại tiếp tục gây Aero DMG liên tục. Trang bị Echo này ở vị trí chính sẽ tăng Aero DMG và Sát Thương Heavy Attack.</t>
+          <t>Triệu hồi Ác Mộng: Feilian Beringal to deal Aero DMG to enemies. The remaining Whirlwind Beam deals continuous Aero DMG. Equipping this Echo in the main slot grants Aero DMG Bonus and Heavy Attack DMG Bonus.</t>
         </is>
       </c>
     </row>
@@ -14992,8 +14992,8 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Biến Đổi Nightmare: Impermanence Heron và tung ra tối đa 10 đòn liên tiếp vào kẻ địch xung quanh, mỗi đòn gây {0} Havoc DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Havoc DMG Bonus và {2} Tăng Sát Thương Heavy Attack.
+          <t>Biến hình Nightmare: Impermanence Heron và tung ra tối đa 10 đòn liên tiếp vào kẻ địch xung quanh, mỗi đòn gây {0} Sát Thương Havoc.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Tăng Sát Thương Havoc và {2} Tăng Sát Thương Đòn Nặng.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -15059,7 +15059,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Biến Đổi Nightmare: Impermanence Heron và gây Havoc DMG cho kẻ địch. Trang bị Echo này ở vị trí chính sẽ tăng Havoc DMG và Sát Thương Heavy Attack.</t>
+          <t>Biến hình Nightmare: Impermanence Heron and deal Havoc DMG to enemies. Equipping this Echo in the main slot grants Havoc DMG Bonus and Heavy Attack DMG Bonus.</t>
         </is>
       </c>
     </row>
@@ -15126,8 +15126,8 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Biến thành Nightmare: Thundering Mephis và tấn công kẻ địch phía trước, gây {0} Electro DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Electro DMG Bonus và {2} Tăng Sát Thương Resonance Liberation.
+          <t>Biến hình thành Ác Mộng: Thundering Mephis và tấn công kẻ địch phía trước, gây {0} Sát Thương Electro.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Tăng Sát Thương Electro và {2} Tăng Sát Thương Resonance Liberation.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Biến thành Nightmare: Thundering Mephis và gây Electro DMG lên kẻ địch. Trang bị Echo này ở vị trí chính sẽ tăng Electro DMG và Sát Thương Resonance Liberation.</t>
+          <t>Biến hình thành Ác Mộng: Thundering Mephis and deal Electro DMG to enemies. Equipping this Echo in the main slot grants Electro DMG Bonus and Resonance Liberation DMG Bonus.</t>
         </is>
       </c>
     </row>
@@ -15260,8 +15260,8 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Biến thành Nightmare: Tempest Mephis và tấn công kẻ địch xung quanh, gây {0} Electro DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Electro DMG Bonus và {2} Tăng Sát Thương Resonance Skill.
+          <t>Biến hình thành Ác Mộng: Tempest Mephis và tấn công kẻ địch xung quanh, gây {0} Sát Thương Electro.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Tăng Sát Thương Electro và {2} Tăng Sát Thương Resonance Skill.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Biến thành Nightmare: Tempest Mephis và gây Electro DMG lên kẻ địch. Trang bị Echo này ở vị trí chính sẽ tăng Electro DMG và Sát Thương Resonance Skill.</t>
+          <t>Biến hình thành Ác Mộng: Tempest Mephis and deal Electro DMG to enemies. Equipping this Echo in the main slot grants Electro DMG Bonus and Resonance Skill DMG Bonus.</t>
         </is>
       </c>
     </row>
@@ -15394,8 +15394,8 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Biến Đổi Nightmare: Crownless và tấn công kẻ địch phía trước, gây {0} Havoc DMG. Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Havoc DMG Bonus và {2} Tăng Sát Thương Basic Attack.
-Kỹ năng này có {3} lần sử dụng ban đầu, hồi lại sau mỗi {4} giây, tối đa {5} lần. Khi Nightmare: Crownless trúng mục tiêu, sát thương của kỹ năng sẽ tăng thêm {6}. Hiệu ứng kéo dài {7} giây và không cộng dồn.
+          <t>Biến hình Nightmare: Crownless và tấn công kẻ địch phía trước, gây {0} Sát Thương Havoc. Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Tăng Sát Thương Havoc và {2} Tăng Sát Thương Đòn Cơ Bản.
+Kỹ năng này có {3} lần sử dụng ban đầu, hồi lại sau mỗi {4} giây, tối đa {5} lần. Khi Nightmare: Crownless trúng mục tiêu, DMG của kỹ năng sẽ tăng thêm {6}. Hiệu ứng kéo dài {7} giây và không cộng dồn.
 Hồi chiêu: {4} giây.</t>
         </is>
       </c>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Biến Đổi Nightmare: Crownless và gây Havoc DMG cho kẻ địch. Trang bị Echo này ở vị trí chính sẽ tăng Havoc DMG và Sát Thương Basic Attack.</t>
+          <t>Biến hình Nightmare: Crownless and deal Havoc DMG to enemies. Equipping this Echo in the main slot grants Havoc DMG Bonus and Basic Attack DMG Bonus.</t>
         </is>
       </c>
     </row>
@@ -15529,9 +15529,9 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Biến Đổi Nightmare: Inferno Rider và nhảy lên tấn công kẻ địch phía trước, gây {0} Fusion DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Fusion DMG Bonus và {2} Tăng Sát Thương Resonance Skill.
-Giữ Kỹ Năng Echo để biến hình thành Nightmare: Inferno Rider và vào Chế Độ Cưỡi. Khi thoát Chế Độ Cưỡi, gây {3} Fusion DMG cho kẻ địch phía trước.
+          <t>Biến hình Nightmare: Inferno Rider và nhảy lên tấn công kẻ địch phía trước, gây {0} Sát Thương Fusion.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Tăng Sát Thương Fusion và {2} Tăng Sát Thương Resonance Skill.
+Giữ Kỹ Năng Echo để biến hình thành Nightmare: Inferno Rider và vào Chế Độ Cưỡi. Khi thoát Chế Độ Cưỡi, gây {3} Sát Thương Fusion cho kẻ địch phía trước.
 Hồi chiêu: {4} giây.</t>
         </is>
       </c>
@@ -15598,8 +15598,8 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Biến Đổi Nightmare: Inferno Rider và gây Fusion DMG cho kẻ địch. Trang bị Echo này ở vị trí chính sẽ tăng Fusion DMG và Sát Thương Resonance Skill.
-Giữ Kỹ Năng Echo để biến hình thành Nightmare: Inferno Rider và vào Chế Độ Cưỡi.</t>
+          <t>Biến hình Nightmare: Inferno Rider and deal Fusion DMG to enemies. Equipping this Echo in the main slot grants Fusion DMG Bonus and Resonance Skill DMG Bonus.
+Hold Echo Skill to transform into Nightmare: Inferno Rider and enter Riding Mode.</t>
         </is>
       </c>
     </row>
@@ -15666,8 +15666,8 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Summon Nightmare: Mourning Aix tấn công kẻ địch xung quanh, gây {0} Spectro DMG. Sát thương gây ra lên kẻ địch bị Spectro Frazzle tăng thêm {1}.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {2} Spectro DMG Bonus.
+          <t>Triệu hồi Ác Mộng: Mourning Aix tấn công kẻ địch xung quanh, gây {0} DMG Spectro. DMG gây ra lên kẻ địch bị Spectro Frazzle tăng thêm {1}.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {2} Tăng Sát Thương Spectro.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -15733,7 +15733,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Summon Nightmare: Mourning Aix gây Spectro DMG lên kẻ địch. Gây sát thương tăng lên đối với kẻ địch bị Spectro Frazzle. Trang bị Echo này ở vị trí chính sẽ tăng Spectro DMG.</t>
+          <t>Triệu hồi Ác Mộng: Mourning Aix to deal Spectro DMG to enemies. Deal increased DMG to enemies inflicted by Spectro Frazzle. Equipping this Echo in the main slot grants Spectro DMG Bonus.</t>
         </is>
       </c>
     </row>
@@ -15800,8 +15800,8 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Summon Nightmare: Lampylumen Myriad tấn công kẻ địch xung quanh, gây {0} Glacio DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {1} Glacio DMG Bonus và gây thêm {2} Sát Thương Đòn Phối Hợp.
+          <t>Triệu hồi Ác Mộng: Lampylumen Myriad tấn công kẻ địch xung quanh, gây {0} Sát Thương Glacio.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {1} Tăng Sát Thương Glacio và gây thêm {2} Sát Thương Đòn Phối Hợp.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -15867,7 +15867,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Summon Nightmare: Lampylumen Myriad và gây Glacio DMG lên kẻ địch gần đó. Trang bị Echo này ở vị trí chính sẽ tăng Glacio DMG và Sát Thương Đòn Phối Hợp.</t>
+          <t>Triệu hồi Ác Mộng: Lampylumen Myriad and deal Glacio DMG to nearby enemies. Equipping this Echo in the main slot grants Glacio DMG Bonus and increases Coordinated Attack DMG.</t>
         </is>
       </c>
     </row>
@@ -15934,8 +15934,8 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Summon Windcleaver tấn công mục tiêu, gây {0} Aero DMG 8 lần và {1} Aero DMG 1 lần.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {2} Aero DMG Bonus. Khi Resonator: Aero hoặc Cartethyia trang bị Echo này, họ sẽ nhận thêm {3} Aero DMG Bonus nữa.
+          <t>Triệu hồi Windcleaver tấn công mục tiêu, gây {0} Sát Thương Aero 8 lần và {1} Sát Thương Aero 1 lần.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {2} Tăng Sát Thương Aero. Khi Resonator: Aero hoặc Cartethyia trang bị Echo này, họ sẽ nhận thêm {3} Tăng Sát Thương Aero nữa.
 Hồi chiêu: {4} giây.</t>
         </is>
       </c>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Summon Windercleaver gây Aero DMG. Trang bị Echo này ở vị trí chính sẽ tăng Aero DMG. Nếu Rover trang bị là Rover: Aero hoặc Cartethyia, sẽ nhận thêm Aero DMG Bonus.</t>
+          <t>Triệu hồi Windercleaver gây Sát Thương Aero. Trang bị Echo này ở vị trí chính sẽ tăng Sát Thương Aero. Nếu Vận Mệnh Giả trang bị là Rover: Aero hoặc Cartethyia, sẽ nhận thêm Tăng Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -16068,8 +16068,8 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Biến thành Nightmare: Kelpie để tấn công mục tiêu lân cận, gây {0} Glacio DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận {2} Glacio DMG Bonus và {3} Aero DMG Bonus. Khi thay đổi Resonator bằng Outro Skill, Nightmare: Kelpie sẽ xuất hiện và gây {1} Aero DMG.
+          <t>Biến hình thành Ác Mộng: Kelpie để tấn công mục tiêu lân cận, gây {0} Sát Thương Glacio.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận {2} Tăng Sát Thương Glacio và {3} Tăng Sát Thương Aero. Khi thay đổi Resonator bằng Kỹ Năng Outro, Ác Mộng: Kelpie sẽ xuất hiện và gây {1} Sát Thương Aero.
 Hồi chiêu: {4} giây</t>
         </is>
       </c>
@@ -16136,8 +16136,8 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Biến Đổi Nightmare: Kelpie để tấn công mục tiêu gần đó, gây Glacio DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận Glacio DMG Bonus và Aero. Khi thay đổi Resonator bằng Outro Skill, triệu hồi Nightmare: Kelpie gây Aero DMG.</t>
+          <t>Biến hình Nightmare: Kelpie to attack nearby targets, dealing Glacio DMG.
+The Resonator with this Echo equipped in the main slot gains Glacio and Aero DMG Bonus. Switching out the Resonator with Outro Skill summons Nightmare: Kelpie to deal Aero DMG.</t>
         </is>
       </c>
     </row>
@@ -16204,8 +16204,8 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Summon Halberd of Glory đè nát khu vực, gây {0} Fusion DMG lên mục tiêu xung quanh, sau đó bùng nổ sau một khoảng thời gian ngắn, gây {1} Fusion DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận {2} Fusion DMG Bonus và {3} Tăng Sát Thương Resonance Liberation.
+          <t>Triệu hồi Halberd of Glory đè nát khu vực, gây {0} Sát Thương Fusion lên mục tiêu xung quanh, sau đó bùng nổ sau một khoảng thời gian ngắn, gây {1} Sát Thương Fusion.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận {2} Tăng Sát Thương Fusion và {3} Tăng Sát Thương Resonance Liberation.
 Hồi chiêu: {4} giây.</t>
         </is>
       </c>
@@ -16272,8 +16272,8 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Summon Halberd of Glory gây Fusion DMG lên mục tiêu xung quanh.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận Fusion DMG Bonus và Resonance Liberation.</t>
+          <t>Triệu hồi Halberd of Glory gây Sát Thương Fusion lên mục tiêu xung quanh.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận Tăng Sát Thương Fusion và Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -16340,8 +16340,8 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Biến Đổi Nightmare: Hecate. Nhảy lên và đập xuống, gây 3 giai đoạn sát thương, mỗi giai đoạn gây Havoc DMG bằng {0} Tấn Công của cô.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Havoc DMG Bonus và {2} Tăng Sát Thương Kỹ Năng Echo.
+          <t>Biến hình Nightmare: Hecate. Nhảy lên và đập xuống, gây 3 giai đoạn DMG, mỗi giai đoạn gây Sát Thương Havoc bằng {0} ATK của cô.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Tăng Sát Thương Havoc và {2} Tăng Sát Thương Kỹ Năng Echo.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -16408,8 +16408,8 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Biến Đổi Nightmare: Hecate. Nhảy lên và đập xuống, gây 3 giai đoạn Havoc DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận Havoc DMG Bonus và Tăng Sát Thương Kỹ Năng Echo.</t>
+          <t>Biến hình Nightmare: Hecate. Nhảy lên và đập xuống, gây 3 giai đoạn Sát Thương Havoc.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận Tăng Sát Thương Havoc và Tăng Sát Thương Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -16476,8 +16476,8 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Summon Talons of Decree tấn công kẻ địch gần đó, gây {0} Aero DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Aero DMG Bonus và {2} Tăng Sát Thương Heavy Attack.
+          <t>Triệu hồi Talons of Decree tấn công kẻ địch gần đó, gây {0} Sát Thương Aero.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận {1} Tăng Sát Thương Aero và {2} Tăng Sát Thương Đòn Nặng.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -16544,8 +16544,8 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Summon Talons of Decree gây Aero DMG lên kẻ địch gần đó.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận Aero DMG Bonus và Heavy Attack.</t>
+          <t>Triệu hồi Talons of Decree gây Sát Thương Aero lên kẻ địch gần đó.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận Tăng Sát Thương Aero và Đòn Nặng.</t>
         </is>
       </c>
     </row>
@@ -16675,7 +16675,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Tấn Công%</t>
+          <t>ATK%</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>% Phòng Ngự</t>
+          <t>DEF%</t>
         </is>
       </c>
     </row>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Phòng Ngự Cơ Bản</t>
+          <t>Base DEF</t>
         </is>
       </c>
     </row>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Tăng lượng Resonance Energy nhận được khi sử dụng Normal Attack, Resonance Skill, Forte Circuit và Intro Skill.</t>
+          <t>Increases the amount of Resonance Energy gained when using Normal Attack, Resonance Skill, Forte Circuit, and Intro Skill.</t>
         </is>
       </c>
     </row>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Tăng cường hiệu quả của Resonance Energy.</t>
+          <t>Boosts the effect of Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -17000,7 +17000,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>HP Cơ Bản</t>
+          <t>Base HP</t>
         </is>
       </c>
     </row>
@@ -17065,7 +17065,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Basic Attack</t>
+          <t>Base ATK</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17130,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Gây Sát Thương bằng Basic Attack hoặc Heavy Attack sẽ tăng Attack thêm {0} và cộng thêm {0} Sát Thương Heavy Attack trong {2} giây, tối đa {1} lần tích lũy. Hiệu ứng này có thể kích hoạt &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=4} mỗi {3} giây.</t>
+          <t>Gây Sát Thương bằng Đòn Basic Attack hoặc Đòn Heavy Attack sẽ tăng ATK thêm {0} và cộng thêm {0} Sát Thương Đòn Heavy Attack trong {2} giây, tối đa {1} lần tích lũy. Hiệu ứng này có thể kích hoạt &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=4} mỗi {3} giây.</t>
         </is>
       </c>
     </row>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Xác suất gây ra Critical Hit khi tấn công.</t>
+          <t>The chance of triggering a Critical Hit when dealing damage.</t>
         </is>
       </c>
     </row>
@@ -17260,7 +17260,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Hệ số Sát Thương khi kích hoạt Đòn Critical Hit.</t>
+          <t>The DMG Multiplier when triggering a Critical Hit.</t>
         </is>
       </c>
     </row>
@@ -17325,7 +17325,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Giữ Basic Attack và quan sát con trỏ di chuyển trên Thanh Forte</t>
+          <t>Giữ Đòn Basic Attack và quan sát con trỏ di chuyển trên Thanh Forte</t>
         </is>
       </c>
     </row>
@@ -17390,7 +17390,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Hồi phục 1 Độ Đo Forte cho Basic Attack khi trúng mục tiêu</t>
+          <t>Hồi phục 1 Độ Đo Forte cho Đòn Cơ Bản khi trúng mục tiêu</t>
         </is>
       </c>
     </row>
@@ -17455,7 +17455,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Resonance Skill hoặc Heavy Attack tiêu hao Thanh Forte để hồi phục HP.</t>
+          <t>Kỹ năng Cộng Hưởng hoặc Đòn Heavy Attack tiêu hao Thanh Forte để hồi phục HP.</t>
         </is>
       </c>
     </row>
@@ -17520,7 +17520,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Hồi phục Thanh Forte khi Resonance Skill Được Tăng Cường, Intro Skill hoặc Resonance Liberation được kích hoạt</t>
+          <t>Hồi phục Thanh Forte khi Resonance Skill Được Tăng Cường, Kỹ Năng Khởi Động hoặc Resonance Liberation được kích hoạt</t>
         </is>
       </c>
     </row>
@@ -17650,7 +17650,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Heavy Attack - Shift Địa Thế: Khi Năng Lượng Khối Lượng Nghỉ đầy, giữ {0} để vào Wide Field Observation Mode, tăng cường cho Resonators trong đội.</t>
+          <t>Tấn Công Mạnh - Dịch Chuyển Địa Thế: Khi Năng Lượng Khối Lượng Nghỉ đầy, giữ {0} để vào Chế Độ Quan Sát Trường Rộng, tăng cường cho Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Basic Attack - Wide Field Observation Mode: Trong Wide Field Observation Mode, {Cus:Ipt,Touch=bấm PC=press Gamepad=press} {0} + {0} + {0} để tích lũy Relative Momentum.</t>
+          <t>Basic Attack - Chế Độ Quan Sát Trường Rộng: Trong Chế Độ Quan Sát Trường Rộng, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} + {0} + {0} để tích lũy Động Lượng Tương Đối.</t>
         </is>
       </c>
     </row>
@@ -17780,7 +17780,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Heavy Attack - Đảo Chiều: Khi Relative Momentum đầy, giữ {0} để tăng sát thương gây ra cho mục tiêu.</t>
+          <t>Tấn Công Mạnh - Đảo Chiều: Khi Động Lượng Tương Đối đầy, giữ {0} để tăng DMG gây ra cho mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -17845,7 +17845,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Resonance Liberation - Critical Protocol: {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để kích hoạt kỹ năng này.</t>
+          <t>Resonance Liberation - Giao Thức Bạo Kích: {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để kích hoạt kỹ năng này.</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Tạo ra một &lt;color=Highlight&gt;Syntony Field&lt;/color&gt; giúp phục hồi HP và tăng &lt;color=Highlight&gt;Off-Tune Buildup Rate&lt;/color&gt;.</t>
+          <t>Tạo ra một &lt;color=Highlight&gt;Trường Cộng Hưởng&lt;/color&gt; giúp phục hồi HP và tăng &lt;color=Highlight&gt;Tốc Độ Tích Lũy Lệch Nhịp&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Gây hiệu ứng &lt;color=Highlight&gt;Interfered Marker&lt;/color&gt;, làm tăng sát thương mục tiêu phải chịu.</t>
+          <t>Gây hiệu ứng &lt;color=Highlight&gt;Dấu Hiệu Giao Thoa&lt;/color&gt;, làm tăng DMG mục tiêu phải chịu.</t>
         </is>
       </c>
     </row>
@@ -18040,7 +18040,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Outro Skill ban &lt;color=Highlight&gt;Tất cả DMG Amplification&lt;/color&gt; cho Resonators trong đội.</t>
+          <t>Kỹ Năng Outro ban &lt;color=Highlight&gt;Khuếch Đại Sát Thương Toàn Bộ&lt;/color&gt; cho các Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -18105,7 +18105,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Trigram - Sơn nhận được khi &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt; gây sát thương. Trigram - Lôi nhận được khi &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt; hoặc &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; gây sát thương hoặc khi &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được sử dụng.</t>
+          <t>Quẻ - Sơn nhận được khi &lt;color=Highlight&gt;Đòn Basic Attack Giai Đoạn 2&lt;/color&gt; gây sát thương. Quẻ - Lôi nhận được khi &lt;color=Highlight&gt;Đòn Basic Attack Giai Đoạn 4&lt;/color&gt; hoặc &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không&lt;/color&gt; gây sát thương hoặc khi &lt;color=Highlight&gt;Kỹ Năng Đồng Điệu&lt;/color&gt; được sử dụng.</t>
         </is>
       </c>
     </row>
@@ -18170,7 +18170,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Các đòn Tấn Công Nặng Special có thể được tung ra bằng cách tiêu hao Trigram - Sơn và Trigram - Lôi. Các chuỗi và tổ hợp Trigram khác nhau sẽ kích hoạt các loại Tấn Công Nặng khác nhau, mang lại hoặc là Âm Khí Nhỏ hoặc Dương Khí Nhỏ.</t>
+          <t>Các đòn Heavy Attack Đặc Biệt có thể được tung ra bằng cách tiêu hao Quẻ - Sơn và Quẻ - Lôi. Các chuỗi và tổ hợp Quẻ khác nhau sẽ kích hoạt các loại Heavy Attack khác nhau, mang lại hoặc là Âm Khí Nhỏ hoặc Dương Khí Nhỏ.</t>
         </is>
       </c>
     </row>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Khi Buling đồng thời sở hữu Minor Yin và Minor Yang, &lt;color=Highlight&gt;Resonance Liberation - Flashing Thunder Spell&lt;/color&gt; của cô sẽ được thay thế bằng &lt;color=Highlight&gt;Resonance Liberation - Flashing Thunder Spell: Harmony&lt;/color&gt;. Sử dụng kỹ năng sẽ tạo ra &lt;color=Highlight&gt;Five Thunders Spell Array&lt;/color&gt; liên tục gây &lt;color=Highlight&gt;Electro Flare&lt;/color&gt; lên mục tiêu.</t>
+          <t>Khi Buling đồng thời sở hữu Minor Yin và Minor Yang, &lt;color=Highlight&gt;Kỹ Năng Resonance Liberation - Phép Thuật Sấm Chớp&lt;/color&gt; của cô sẽ được thay thế bằng &lt;color=Highlight&gt;Kỹ Năng Resonance Liberation - Phép Thuật Sấm Chớp: Hòa Điệu&lt;/color&gt;. Sử dụng kỹ năng sẽ tạo ra &lt;color=Highlight&gt;Mảng Phép Thuật Ngũ Lôi&lt;/color&gt; liên tục gây &lt;color=Highlight&gt;Electro Flare&lt;/color&gt; lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -18300,7 +18300,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Five Thunders Spell Array&lt;/color&gt; đang hoạt động, mỗi khi bất kỳ Resonator nào trong đội sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt;, Resonator đang hoạt động trong đội sẽ nhận được Buff Tăng Sát Thương.</t>
+          <t>Khi &lt;color=Highlight&gt;Bát Quái Trận Pháp Lôi&lt;/color&gt; đang hoạt động, mỗi khi bất kỳ Resonator nào trong đội sử dụng &lt;color=Highlight&gt;Kỹ Năng Intro&lt;/color&gt;, Resonator đang hoạt động trong đội sẽ nhận được Buff Tăng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -18365,7 +18365,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Heal và tăng Sát Thương cho Resonators trong đội.</t>
+          <t>Hồi phục và tăng Sát Thương cho Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -18495,7 +18495,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Khi Resonance Liberation đang hoạt động, bất kỳ Resonators nào trong đội sử dụng Kỹ Năng Giới Thiệu sẽ ban thêm Hiệu Ứng Tăng Sát Thương cho Resonators trong đội.</t>
+          <t>Khi Resonance Liberation đang hoạt động, bất kỳ Resonator nào trong đội sử dụng Kỹ Năng Giới Thiệu sẽ ban thêm Hiệu Ứng Tăng Sát Thương cho các Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -18611,8 +18611,8 @@
 Tiêu hao STA để thực hiện Mid-air Attack, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-- Sau khi thực hiện &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+- Sau khi thực hiện &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Trigram&lt;/color&gt;&lt;/size&gt;
 Buling có thể giữ tối đa {4} quẻ. Khi số quẻ đạt tối đa, nhận thêm quẻ mới sẽ đẩy tất cả quẻ sang trái {5} ô, và quẻ ngoài cùng bên trái sẽ bị loại bỏ.
@@ -18802,7 +18802,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill sẽ tăng Attack {0} và tăng Sát Thương Basic Attack {0} trong {1} giây.</t>
+          <t>Kích hoạt Resonance Skill sẽ tăng ATK {0} và tăng Sát Thương Basic Attack {0} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -18867,7 +18867,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Hồi phục Thanh Forte khi Normal Attack trúng mục tiêu hoặc khi Intro Skill được kích hoạt</t>
+          <t>Hồi phục Thanh Forte khi Đòn Normal Attack trúng mục tiêu hoặc khi Kỹ Năng Khởi Động được kích hoạt</t>
         </is>
       </c>
     </row>
@@ -18997,7 +18997,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Giữ nút Normal Attack để nạp Thanh Forte. Khi Thanh Forte đầy, thả ra để thi triển Heavy Attack và nhận một Món Đồ Cổ ngẫu nhiên.</t>
+          <t>Giữ nút Normal Attack để nạp Thanh Forte. Khi Thanh Forte đầy, thả ra để thi triển Đòn Heavy Attack và nhận một Món Đồ Cổ ngẫu nhiên.</t>
         </is>
       </c>
     </row>
@@ -19064,7 +19064,7 @@
       <c r="M266" t="inlineStr">
         <is>
           <t>Với một Đồ Cổ, chạm để sử dụng Đánh Giá Đồ Cổ tương ứng và nhận được Auspices phù hợp.
-Khi đạt bốn Auspices, giữ Normal Attack để sử dụng Poetic Essence. Hiệu ứng bổ sung sẽ được kích hoạt dựa trên tổ hợp Auspices.</t>
+Khi đạt bốn Auspices, giữ Đòn Normal Attack để sử dụng Poetic Essence. Hiệu ứng bổ sung sẽ được kích hoạt dựa trên tổ hợp Auspices.</t>
         </is>
       </c>
     </row>
@@ -19195,8 +19195,8 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Nhận Tinh Thể Dẻo khi sử dụng các kỹ năng khác nhau, bao gồm Intro Skill, Resonance Skill và Heavy Attack.
-Dùng Intro Skill hoặc Dodge Counter, hoặc tiêu thụ Tinh Thể Dẻo để hồi phục Thanh Forte.</t>
+          <t>Nhận Tinh Thể Dẻo khi sử dụng các kỹ năng khác nhau, bao gồm Kỹ Năng Khởi Động, Resonance Skill và Đòn Tấn Công Mạnh.
+Dùng Kỹ Năng Khởi Động hoặc Dodge Counter Tránh, hoặc tiêu thụ Tinh Thể Dẻo để hồi phục Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -19262,7 +19262,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Tiêu hao Substance để tăng Hệ Số Sát Thương của Resonance Liberation hoặc tung đòn Heavy Attack - Cận Kề Hư Vô, giúp giảm Cooldown chiêu Resonance Skill.
+          <t>Tiêu hao Substance để tăng Hệ Số Sát Thương của Resonance Liberation hoặc tung đòn Heavy Attack - Cận Kề Hư Vô, giúp giảm thời gian hồi chiêu Resonance Skill.
 Các đòn Resonance Liberation sẽ hồi phục Meta Vector khi trúng mục tiêu. Resonance Liberation - Đoạn Kết Chí Mạng sẽ khả dụng khi Meta Vector đầy.</t>
         </is>
       </c>
@@ -19328,7 +19328,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Normal Attack, Resonance Skill và Intro Skill hồi phục Thanh Forte khi trúng mục tiêu</t>
+          <t>Normal Attack, Resonance Skill và Kỹ Năng Khởi Động hồi phục Thanh Forte khi trúng mục tiêu</t>
         </is>
       </c>
     </row>
@@ -19458,7 +19458,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Giữ Basic Attack ở trạng thái bình thường khi Thanh Forte đầy để thi triển Heavy Attack được tăng cường</t>
+          <t>Giữ Đòn Basic Attack ở trạng thái bình thường khi Thanh Forte đầy để thi triển Đòn Tấn Công Mạnh được tăng cường</t>
         </is>
       </c>
     </row>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Giữ Basic Attack trong trạng thái Resonance Liberation khi Thanh Forte đầy để thi triển Đòn Resonance Liberation được tăng cường</t>
+          <t>Giữ Đòn Basic Attack trong trạng thái Resonance Liberation khi Thanh Forte đầy để thi triển Đòn Resonance Liberation được tăng cường</t>
         </is>
       </c>
     </row>
@@ -19588,7 +19588,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Normal Attack, Resonance Skill và Intro Skill hồi phục Thanh Forte khi trúng mục tiêu</t>
+          <t>Normal Attack, Resonance Skill và Kỹ Năng Khởi Động hồi phục Thanh Forte khi trúng mục tiêu</t>
         </is>
       </c>
     </row>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 1 Basic Attack</t>
+          <t>DMG Giai đoạn 1 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 2 Basic Attack</t>
+          <t>DMG Giai đoạn 2 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 3 Basic Attack</t>
+          <t>DMG Giai đoạn 3 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 4 của Basic Attack</t>
+          <t>Sát Thương Cú Đòn Cơ Bản Hạng 4</t>
         </is>
       </c>
     </row>
@@ -19978,7 +19978,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 1 DMG Wide Field Observation Mode</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 1 Chế Độ Quan Sát Trường Rộng</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 2 DMG Wide Field Observation Mode</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 2 Chế Độ Quan Sát Trường Rộng</t>
         </is>
       </c>
     </row>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Basic Attack - Stage 3 DMG Wide Field Observation Mode</t>
+          <t>Basic Attack - Sát Thương Giai Đoạn 3 Chế Độ Quan Sát Trường Rộng</t>
         </is>
       </c>
     </row>
@@ -20173,7 +20173,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -20368,7 +20368,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -20498,7 +20498,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Healing Mảng Phân Bố</t>
+          <t>Hồi Phục Mảng Phân Bố</t>
         </is>
       </c>
     </row>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -20628,7 +20628,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Healing Lỗi Kỳ Vọng</t>
+          <t>Hồi Phục Lỗi Kỳ Vọng</t>
         </is>
       </c>
     </row>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -20823,7 +20823,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Sát Thương Mảng Phân Phối</t>
+          <t>Sát Thương Mảng Phân Bố</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Cooldown Lỗi Kỳ Vọng</t>
+          <t>Thời gian hồi Phục Lỗi Kỳ Vọng</t>
         </is>
       </c>
     </row>
@@ -21083,7 +21083,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Cooldown Bản Hòa Tấu Mảng Phân Tán</t>
+          <t>Hồi Chiêu Bản Hòa Tấu Mảng Phân Tán</t>
         </is>
       </c>
     </row>
@@ -21213,7 +21213,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Concerto Regen Mảng Phân Phối</t>
+          <t>Hồi Phục Bản Hòa Tấu Mảng Phân Tán</t>
         </is>
       </c>
     </row>
@@ -21278,7 +21278,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>{0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -21343,7 +21343,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -21408,7 +21408,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Tiêu hao Resonance Energy</t>
+          <t>Chi Phí Resonance Energy</t>
         </is>
       </c>
     </row>
@@ -21733,7 +21733,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -21863,7 +21863,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Hồi phục Syntony Field</t>
+          <t>Hồi phục Trường Điều Tần</t>
         </is>
       </c>
     </row>
@@ -21928,7 +21928,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Tăng {0} DEF</t>
+          <t>Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -21993,7 +21993,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Sát thương Syntony Field</t>
+          <t>DMG Trường Điều Tần</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sát Thương Shift Địa Thế</t>
+          <t>Tấn Công Mạnh - Sát Thương Dịch Chuyển Địa Thế</t>
         </is>
       </c>
     </row>
@@ -22123,7 +22123,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sát Thương Đảo Chiều</t>
+          <t>Tấn Công Mạnh - Sát Thương Đảo Chiều</t>
         </is>
       </c>
     </row>
@@ -22188,7 +22188,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Tune Rupture Response - Sát thương Particle Jet</t>
+          <t>Phản ứng Tune Rupture - DMG Particle Jet</t>
         </is>
       </c>
     </row>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>{0} Tune AMP</t>
+          <t>{0} Điều chỉnh AMP</t>
         </is>
       </c>
     </row>
@@ -22318,7 +22318,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Chi Phí STA Mỗi Giây Cho Wide Field Observation Mode</t>
+          <t>Chi Phí STA Mỗi Giây Cho Chế Độ Quan Sát Trường Rộng</t>
         </is>
       </c>
     </row>
@@ -22383,7 +22383,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Dodge Phản Công - Sát Thương Chế Độ Quan Sát Diện Rộng</t>
+          <t>Né Tránh Phản Công - Sát Thương Chế Độ Quan Sát Diện Rộng</t>
         </is>
       </c>
     </row>
@@ -22448,7 +22448,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Heavy Attack - Sấm Chớp Vùi Núi Tiêu Hao Thể Lực</t>
+          <t>Heavy Attack - Sấm Chớp Vùi Núi Tiêu Hao STA</t>
         </is>
       </c>
     </row>
@@ -22643,7 +22643,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Heavy Attack - Khúc Giao Hưởng Núi Vượt Sấm: Hồi Phục</t>
+          <t>Tấn Công Mạnh - Khúc Giao Hưởng Núi Vượt Sấm: Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -22708,7 +22708,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Sát Thương Bùa Sấm</t>
+          <t>Sát Thương Bùa Lôi</t>
         </is>
       </c>
     </row>
@@ -22903,7 +22903,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -23033,7 +23033,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Tấn Công Thường, Resonance Skill và Intro Skill hồi phục Thanh Forte khi trúng mục tiêu.</t>
+          <t>Normal Attack, Resonance Skill và Kỹ Năng Khởi Động hồi phục Thanh Forte khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -23098,7 +23098,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Khi nhận được một lượng nhất định Forte Gauge, hồi phục HP một lần cho tất cả Resonators trong đội. Khi Forte Gauge được hồi đầy, nhấn nút Resonance Skill để thực hiện Resonance Skill được tăng cường.</t>
+          <t>Khi nhận được một lượng nhất định Forte Gauge, hồi phục HP một lần cho tất cả Resonator trong đội. Khi Forte Gauge được hồi đầy, nhấn nút Resonance Skill để thực hiện Resonance Skill được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -23163,7 +23163,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu sẽ hồi phục Thanh Wolflame. Khi Wolflame đạt tối thiểu 50 điểm, Heavy Attack và Đòn Mid-air Attack Trọng Lực Cấp 3 sẽ hồi phục Wolfaith bằng cách tiêu hao Wolflame.</t>
+          <t>Đánh trúng mục tiêu sẽ hồi phục Thanh Wolflame. Khi Wolflame đạt tối thiểu 50 điểm, Đòn Tấn Công Mạnh và Đòn Tấn Công Giữa Không Trọng Lực Cấp 3 sẽ hồi phục Wolfaith bằng cách tiêu hao Wolflame.</t>
         </is>
       </c>
     </row>
@@ -23228,7 +23228,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Resonance Skill Nâng Cao sẽ khả dụng khi Wolfaith đạt trạng thái đầy đủ.</t>
+          <t>Kỹ năng Cộng Hưởng Nâng Cao sẽ khả dụng khi Wolfaith đạt trạng thái đầy đủ.</t>
         </is>
       </c>
     </row>
@@ -23293,7 +23293,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Resonance Liberation cao và tăng sát thương đầu ra của tất cả Resonators trong đội.</t>
+          <t>Gây Sát Thương Resonance Liberation cao và tăng DMG đầu ra của tất cả Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -23358,7 +23358,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Cho phép tất cả Resonators trong đội bỏ qua Fusion RES. Đội có càng nhiều Resonators Fusion thì hiệu quả càng lớn.</t>
+          <t>Cho phép tất cả Resonator trong đội bỏ qua Kháng Fusion. Đội có càng nhiều Resonator Fusion thì hiệu quả càng lớn.</t>
         </is>
       </c>
     </row>
@@ -23423,7 +23423,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Outro Skill khuếch đại mạnh Fusion DMG và Sát Thương Basic Attack.</t>
+          <t>Kỹ Năng Outro khuếch đại mạnh Sát Thương Fusion và Sát Thương Đòn Cơ Bản.</t>
         </is>
       </c>
     </row>
@@ -23488,7 +23488,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Heavy Attack - Volley of Death&lt;/color&gt;: Giữ {0} để bắn liên tiếp 3 phát.</t>
+          <t>&lt;color=Highlight&gt;Đòn Heavy Attack - Loạt Tử Thần&lt;/color&gt;: Giữ {0} để bắn liên tiếp 3 phát.</t>
         </is>
       </c>
     </row>
@@ -23553,7 +23553,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Threshold State&lt;/color&gt;, Galbrena tích lũy &lt;color=Highlight&gt;Sinflame&lt;/color&gt; mỗi khi tấn công trúng mục tiêu. Khi &lt;color=Highlight&gt;Sinflame&lt;/color&gt; đạt 100 điểm, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill để bước vào &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt;.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Trạng Thái Ngưỡng&lt;/color&gt;, Galbrena tích lũy &lt;color=Highlight&gt;Lửa Tội&lt;/color&gt; mỗi khi tấn công trúng mục tiêu. Khi &lt;color=Highlight&gt;Lửa Tội&lt;/color&gt; đạt 100 điểm, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill để bước vào &lt;color=Highlight&gt;Hóa Thân Ác Quỷ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23618,7 +23618,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt;, Galbrena nhận được 100 điểm &lt;color=Highlight&gt;Purging Flame&lt;/color&gt; bằng cách tiêu thụ toàn bộ &lt;color=Highlight&gt;Sinflame&lt;/color&gt;. Khi ở trạng thái &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt;, lượng &lt;color=Highlight&gt;Afterflame&lt;/color&gt; Galbrena sở hữu càng nhiều, kẻ địch càng chịu nhiều sát thương từ &lt;color=Highlight&gt;các chiêu cường hóa khác nhau&lt;/color&gt;.</t>
+          <t>Trong &lt;color=Highlight&gt;Hóa Thân Ác Quỷ&lt;/color&gt;, Galbrena nhận được 100 điểm &lt;color=Highlight&gt;Lửa Thanh Tẩy&lt;/color&gt; bằng cách tiêu thụ toàn bộ &lt;color=Highlight&gt;Lửa Tội&lt;/color&gt;. Khi ở trạng thái &lt;color=Highlight&gt;Hóa Thân Ác Quỷ&lt;/color&gt;, lượng &lt;color=Highlight&gt;Lửa Dư&lt;/color&gt; Galbrena sở hữu càng nhiều, kẻ địch càng chịu nhiều DMG từ &lt;color=Highlight&gt;các đòn tấn công được tăng cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23683,7 +23683,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Khi Resonators trong đội sử dụng Kỹ Năng Vọng Âm, Galbrena nhận được &lt;color=Highlight&gt;Afterflame&lt;/color&gt;, làm tăng sát thương gây ra trong lần &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt; tiếp theo.</t>
+          <t>Khi Resonator trong đội sử dụng Kỹ Năng Vọng Âm, Galbrena nhận được &lt;color=Highlight&gt;Dư Lửa&lt;/color&gt;, làm tăng DMG gây ra trong lần &lt;color=Highlight&gt;Dị Thể Ác Ma&lt;/color&gt; tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -23748,7 +23748,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} Dodge trong khi thực hiện hành động chiến đấu để thi triển &lt;color=Highlight&gt;Hellstride&lt;/color&gt;. Thi triển kỹ năng này sẽ tăng Tấn Công của Galbrena và khả năng chống gián đoạn trong một khoảng thời gian nhất định, đồng thời không làm reset chu kỳ tấn công trong hành động trong thời gian ngắn.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Né Tránh trong khi thực hiện hành động chiến đấu để thi triển &lt;color=Highlight&gt;Bước Địa Ngục&lt;/color&gt;. Thi triển kỹ năng này sẽ tăng ATK của Galbrena và khả năng chống gián đoạn trong một khoảng thời gian nhất định, đồng thời không làm reset chu kỳ tấn công trong hành động trong thời gian ngắn.</t>
         </is>
       </c>
     </row>
@@ -23813,7 +23813,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Các đòn tấn công của Galbrena tích lũy &lt;color=Highlight&gt;Sinflame&lt;/color&gt; khi trúng mục tiêu. Khi &lt;color=Highlight&gt;Sinflame&lt;/color&gt; đạt 100 điểm, {Cus:Ipt,Touch=tấn PC=press Gamepad=press} Resonance Skill để bước vào &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt;.</t>
+          <t>Các đòn tấn công của Galbrena tích lũy &lt;color=Highlight&gt;Lửa Tội&lt;/color&gt; khi trúng mục tiêu. Khi &lt;color=Highlight&gt;Lửa Tội&lt;/color&gt; đạt 100 điểm, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill để bước vào &lt;color=Highlight&gt;Hóa Thân Ác Quỷ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23883,10 +23883,10 @@
       <c r="M340" t="inlineStr">
         <is>
           <t>Khi Prowess đạt tối đa:
-- Giữ {0} để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Backstep&lt;/color&gt;, sau đó thả {0} trong khoảng thời gian nhất định, hoặc {Cus:Ipt,Touch=bấm PC=press Gamepad=press} {0} lần nữa để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Spinslash&lt;/color&gt;.
-- {Cus:Ipt,Touch=Bấm PC=press Gamepad=press} Nhảy để thi triển &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;.
-- Khi thực hiện &lt;color=Highlight&gt;Heavy Attack - Steelclash&lt;/color&gt;, thả {0} trong khoảng thời gian nhất định, hoặc {Cus:Ipt,Touch=bấm PC=press Gamepad=press} {0} lần nữa, hoặc {Cus:Ipt,Touch=bấm PC=press Gamepad=press} Nhảy để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;.
-- Khi thi triển &lt;color=Highlight&gt;Resonance Skill - Warrior's Blade&lt;/color&gt;, {Cus:Ipt,Touch=bấm PC=press Gamepad=press} {1} hoặc Nhảy để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;.</t>
+- Giữ {0} để thực hiện &lt;color=Highlight&gt;Đòn Heavy Attack - Thunderoar: Backstep&lt;/color&gt;, sau đó thả {0} trong khoảng thời gian nhất định, hoặc {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} lần nữa để thực hiện &lt;color=Highlight&gt;Đòn Heavy Attack - Thunderoar: Spinslash&lt;/color&gt;.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Nhảy để thi triển &lt;color=Highlight&gt;Đòn Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;.
+- Khi thực hiện &lt;color=Highlight&gt;Đòn Heavy Attack - Steelclash&lt;/color&gt;, thả {0} trong khoảng thời gian nhất định, hoặc {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} lần nữa, hoặc {Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy để thực hiện &lt;color=Highlight&gt;Đòn Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;.
+- Khi thi triển &lt;color=Highlight&gt;Resonance Skill - Warrior's Blade&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {1} hoặc Nhảy để thực hiện &lt;color=Highlight&gt;Đòn Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23954,8 +23954,8 @@
       <c r="M341" t="inlineStr">
         <is>
           <t>Khi Thăng Hoa đạt tối đa:
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} {1} + {Cus:Ipt,Touch=tap PC=press Gamepad=press} {1}/{0} + {Cus:Ipt,Touch=tap PC=press Gamepad=press} {1}/{0} để thực hiện các kỹ năng theo thứ tự:
-- &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Strike&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Leap&lt;/color&gt;, và &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Plunge&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {1} + {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {1}/{0} + {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {1}/{0} để thực hiện các kỹ năng theo thứ tự:
+- &lt;color=Highlight&gt;Resonance Skill - Ánh Dương Bất Tử: Đòn Đánh&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Ánh Dương Bất Tử: Nhảy Tấn Công&lt;/color&gt;, và &lt;color=Highlight&gt;Resonance Skill - Ánh Dương Bất Tử: Lao Xuống&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24087,7 +24087,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Augusta tích lũy Uy Lực để tung ra &lt;color=Highlight&gt;Chained Heavy Attacks&lt;/color&gt; và Uy Thế để thi triển &lt;color=Highlight&gt;Chained Resonance Skills&lt;/color&gt;.</t>
+          <t>Augusta tích lũy Uy Lực để tung ra &lt;color=Highlight&gt;Đòn Heavy Attack Liên Hoàn&lt;/color&gt; và Uy Thế để thi triển &lt;color=Highlight&gt;Resonance Skill Liên Hoàn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24152,7 +24152,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Inherent Skill - Blazing Valor&lt;/color&gt;, &lt;color=Highlight&gt;Outro Skill - Battlesong of the Unyielding&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Plunge&lt;/color&gt; sẽ cấp hiệu ứng Oai Phong.</t>
+          <t>&lt;color=Highlight&gt;Kỹ Năng Nội Tại - Dũng Khí Bừng Cháy&lt;/color&gt;, &lt;color=Highlight&gt;Kỹ Năng Outro - Bản Hùng Ca Bất Khuất&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Skill - Ánh Dương Bất Tử: Lao Xuống&lt;/color&gt; sẽ cấp hiệu ứng Oai Phong.</t>
         </is>
       </c>
     </row>
@@ -24347,7 +24347,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Augusta tạo lá chắn cho tất cả Resonators trong đội khi họ sử dụng Intro Skill và cho chính mình khi gây sát thương.</t>
+          <t>Augusta tạo lá chắn cho tất cả Resonator trong đội khi họ sử dụng Kỹ Năng Khởi Động và cho chính mình khi gây sát thương.</t>
         </is>
       </c>
     </row>
@@ -24412,7 +24412,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Outro Skill của nàng sẽ tăng cường sát thương cho Resonator tiếp theo trên mọi thuộc tính.</t>
+          <t>Kỹ Năng Outro của nàng sẽ tăng cường DMG cho Resonator tiếp theo trên mọi thuộc tính.</t>
         </is>
       </c>
     </row>
@@ -24477,7 +24477,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Normal Attack, Resonance Skill và Intro Skill hồi phục Thanh Forte khi trúng mục tiêu</t>
+          <t>Normal Attack, Resonance Skill và Kỹ Năng Khởi Động hồi phục Thanh Forte khi trúng mục tiêu</t>
         </is>
       </c>
     </row>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Enhanced Mid-air Attack, Intro Skill và Normal Attack phục hồi Forte Gauge.</t>
+          <t>Đòn Tấn Công Giữa Không Nâng Cao, Kỹ Năng Khởi Động và Đòn Normal Attack phục hồi Forte Gauge.</t>
         </is>
       </c>
     </row>
@@ -24672,7 +24672,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Sau khi kết thúc Stage 4 của Basic Attack, Ciaccona bắt đầu một &lt;color=Highlight&gt;Solo Concert&lt;/color&gt; với các nhạc cụ khác nhau dựa trên chuỗi đòn tấn công cô đã thực hiện. Khi Stage 4 của Basic Attack và &lt;color=Highlight&gt;Solo Concert&lt;/color&gt; kết thúc chủ động hoặc bị gián đoạn, một &lt;color=Highlight&gt;Ensemble Sylph&lt;/color&gt; sẽ được tạo ra để tiếp tục hành động.</t>
+          <t>Sau khi kết thúc Giai Đoạn 4 của Basic Attack, Ciaccona bắt đầu một &lt;color=Highlight&gt;Buổi Solo&lt;/color&gt; với các nhạc cụ khác nhau dựa trên chuỗi đòn tấn công cô đã thực hiện. Khi Giai Đoạn 4 của Basic Attack và &lt;color=Highlight&gt;Buổi Solo&lt;/color&gt; kết thúc chủ động hoặc bị gián đoạn, một &lt;color=Highlight&gt;Ensemble Sylph&lt;/color&gt; sẽ được tạo ra để tiếp tục hành động.</t>
         </is>
       </c>
     </row>
@@ -24738,7 +24738,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Sử dụng Basic Attack Stage 4 hoặc Intro Skill sẽ hồi phục 1 đoạn Forte Gauge.
+          <t>Sử dụng Đòn Basic Attack Giai Đoạn 4 hoặc Kỹ Năng Khởi Động sẽ hồi phục 1 đoạn Forte Gauge.
 Khi Forte Gauge đầy, sẽ kích hoạt Heavy Attack Nâng Cao.</t>
         </is>
       </c>
@@ -24804,7 +24804,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Sau khi kích hoạt Resonance Liberation, hãy {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút đúng lúc theo chỉ dẫn để tỏa ra &lt;color=Highlight&gt;Symphonic Poem: Tonic&lt;/color&gt;.</t>
+          <t>Sau khi kích hoạt Resonance Liberation, hãy {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút đúng lúc theo chỉ dẫn để tỏa ra &lt;color=Highlight&gt;Khúc Giao Hưởng: Tonic&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24871,8 +24871,8 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Tăng cường thông qua các &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; khác nhau và gia tăng đáng kể sát thương &lt;color=Highlight&gt;Aero Erosion&lt;/color&gt;.
-Gây hiệu ứng &lt;color=Highlight&gt;Aero Erosion&lt;/color&gt; và nhận tăng sát thương mạnh dựa trên số tầng &lt;color=Highlight&gt;Aero Erosion&lt;/color&gt; trên mục tiêu.
+          <t>Tăng cường thông qua các &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; khác nhau và gia tăng đáng kể DMG &lt;color=Highlight&gt;Xói Mòn Aero&lt;/color&gt;.
+Gây hiệu ứng &lt;color=Highlight&gt;Xói Mòn Aero&lt;/color&gt; và nhận tăng DMG mạnh dựa trên số tầng &lt;color=Highlight&gt;Xói Mòn Aero&lt;/color&gt; trên mục tiêu.
 &lt;color=Highlight&gt;Cartethyia&lt;/color&gt; có thể tự do biến hình giữa bản thân và &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt;.</t>
         </is>
       </c>
@@ -24938,7 +24938,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Khi sử dụng &lt;color=Highlight&gt;Cartethyia&lt;/color&gt;: Basic Attack, Heavy Attack, Intro Skill và Resonance Skill cuối cùng của &lt;color=Highlight&gt;Cartethyia&lt;/color&gt; sẽ triệu hồi các &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; khác nhau. Khi có &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; trên chiến trường, Đòn Lao Xuống của &lt;color=Highlight&gt;Cartethyia's&lt;/color&gt; sẽ thu hồi các &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; và gây thêm Sát Thương dựa trên số lượng Bóng Kiếm đã thu hồi.</t>
+          <t>Khi sử dụng &lt;color=Highlight&gt;Cartethyia&lt;/color&gt;: Đòn Basic Attack, Heavy Attack, Kỹ Năng Khởi Động và Resonance Skill cuối cùng của &lt;color=Highlight&gt;Cartethyia&lt;/color&gt; sẽ triệu hồi các &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; khác nhau. Khi có &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; trên chiến trường, Tấn Công Lao Xuống của &lt;color=Highlight&gt;Cartethyia&lt;/color&gt; sẽ thu hồi các &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; và gây thêm Sát Thương dựa trên số lượng Bóng Kiếm đã thu hồi.</t>
         </is>
       </c>
     </row>
@@ -25004,8 +25004,8 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Khi Resonance Energy của &lt;color=Highlight&gt;Cartethyia's&lt;/color&gt; đầy, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Liberation để biến hình thành &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; và nhận các hiệu ứng thưởng khác nhau trong một khoảng thời gian dựa trên số &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; đã thu hồi.
-Dưới dạng &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt;: Các đòn tấn công sẽ hồi phục &lt;color=Highlight&gt;Conviction&lt;/color&gt;. Khi &lt;color=Highlight&gt;Conviction&lt;/color&gt; đạt 120 điểm, &lt;color=Highlight&gt;Resonance Liberation - Blade of Howling Squall&lt;/color&gt; sẽ sẵn sàng sử dụng.</t>
+          <t>Khi Resonance Energy của &lt;color=Highlight&gt;Cartethyia&lt;/color&gt; đầy, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Liberation để biến hình thành &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; và nhận các hiệu ứng thưởng khác nhau trong một khoảng thời gian dựa trên số &lt;color=Highlight&gt;Bóng Kiếm&lt;/color&gt; đã thu hồi.
+Dưới dạng &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt;: Các đòn tấn công sẽ hồi phục &lt;color=Highlight&gt;Lòng Quyết Tâm&lt;/color&gt;. Khi &lt;color=Highlight&gt;Lòng Quyết Tâm&lt;/color&gt; đạt 120 điểm, &lt;color=Highlight&gt;Resonance Liberation - Lưỡi Kiếm Gió Hú&lt;/color&gt; sẽ sẵn sàng sử dụng.</t>
         </is>
       </c>
     </row>
@@ -25070,7 +25070,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Khi Iuno ở trạng thái &lt;color=Highlight&gt;Lunar Cycle - Half Moon&lt;/color&gt;, tấn công sẽ hồi phục Thanh Forte khi trúng mục tiêu.</t>
+          <t>Khi Iuno ở trạng thái &lt;color=Highlight&gt;Chu Kỳ Mặt Trăng - Trăng Khuyết&lt;/color&gt;, tấn công sẽ hồi phục Thanh Forte khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Khi Iuno ở trạng thái &lt;color=Highlight&gt;Lunar Cycle - New Moon&lt;/color&gt;, sử dụng &lt;color=Highlight&gt;Moonbow - Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Arc Beyond the Edge&lt;/color&gt; và &lt;color=Highlight&gt;Moonbow - Dodge Counter&lt;/color&gt; sẽ tiêu hao Thanh Forte.</t>
+          <t>Khi Iuno ở trạng thái &lt;color=Highlight&gt;Chu Kỳ Mặt Trăng - Trăng Non&lt;/color&gt;, sử dụng &lt;color=Highlight&gt;Cung Trăng - Đòn Cơ Bản&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Vòng Cung Vượt Giới&lt;/color&gt; và &lt;color=Highlight&gt;Cung Trăng - Dodge Counter Tránh&lt;/color&gt; sẽ tiêu hao Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -25200,7 +25200,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy, Iuno có thể sử dụng &lt;color=Highlight&gt;Heavy Attack - Absolute Fullness&lt;/color&gt;.</t>
+          <t>Khi Concerto Energy đầy, Iuno có thể sử dụng &lt;color=Highlight&gt;Đòn Heavy Attack - Tuyệt Đối Viên Mãn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25265,7 +25265,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Gây sát thương Resonance Liberation cao, hồi phục HP cho Resonators trong đội và tăng cường sát thương cho những Resonators nhận được Shield.</t>
+          <t>Gây DMG Resonance Liberation cao, hồi phục HP cho các Resonator trong đội và tăng cường DMG cho những Resonator nhận được Khiên.</t>
         </is>
       </c>
     </row>
@@ -25395,7 +25395,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Kỹ Năng Hồi Kết khuếch đại Sát Thương Heavy Attack của Resonator kế tiếp.</t>
+          <t>Kỹ Năng Hồi Kết khuếch đại Sát Thương Đòn Heavy Attack của Resonator kế tiếp.</t>
         </is>
       </c>
     </row>
@@ -25525,7 +25525,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Lời Kiếm Răn Dạy: Tranh Thuỷ Mặc - Khi Swordster's Soliloquy đạt 200 điểm, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để thi triển kỹ năng này. Qiuyuan uống từ ống tre sau mỗi giai đoạn của kỹ năng để nhận thêm Swordster's Soliloquy.</t>
+          <t>Lời Kiếm Răn Dạy: Tranh Thuỷ Mặc - Khi Độc Thoại Kiếm Khách đạt 200 điểm, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để thi triển kỹ năng này. Qiuyuan uống từ ống tre sau mỗi giai đoạn của kỹ năng để nhận thêm Độc Thoại Kiếm Khách.</t>
         </is>
       </c>
     </row>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Lưỡi Kiếm Lên Tiếng: Dạy Dỗ - Trong trạng thái Tâm Thể Loang Mực, giữ {0} để thi triển kỹ năng này, trả giá bằng Swordster's Soliloquy.</t>
+          <t>Lưỡi Kiếm Lên Tiếng: Dạy Dỗ - Trong trạng thái Tâm Thể Loang Mực, giữ {0} để thi triển kỹ năng này, trả giá bằng Độc Thoại Kiếm Khách.</t>
         </is>
       </c>
     </row>
@@ -25655,7 +25655,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Lưỡi Kiếm Lên Tiếng: Cứu Rỗi - Trong trạng thái Tâm Thể Loang Mực, sau khi dùng Lưỡi Kiếm Lên Tiếng: Dạy Dỗ, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để thi triển kỹ năng này, trả giá bằng Swordster's Soliloquy.</t>
+          <t>Lưỡi Kiếm Lên Tiếng: Cứu Rỗi - Trong trạng thái Tâm Thể Loang Mực, sau khi dùng Lưỡi Kiếm Lên Tiếng: Dạy Dỗ, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để thi triển kỹ năng này, trả giá bằng Độc Thoại Kiếm Khách.</t>
         </is>
       </c>
     </row>
@@ -25720,7 +25720,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Lưỡi Kiếm Lên Tiếng: Hy Sinh - Trong trạng thái Tâm Thể Loang Mực, sau khi dùng Lưỡi Kiếm Lên Tiếng: Cứu Rỗi, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để thi triển kỹ năng này, trả giá bằng Swordster's Soliloquy.</t>
+          <t>Lưỡi Kiếm Lên Tiếng: Hy Sinh - Trong trạng thái Tâm Thể Loang Mực, sau khi dùng Lưỡi Kiếm Lên Tiếng: Cứu Rỗi, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để thi triển kỹ năng này, trả giá bằng Độc Thoại Kiếm Khách.</t>
         </is>
       </c>
     </row>
@@ -25785,7 +25785,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Qiuyuan hồi phục &lt;color=Highlight&gt;Swordster's Soliloquy&lt;/color&gt; thông qua Basic Attack Giai đoạn 3 và Dodge Counter. Khi &lt;color=Highlight&gt;Swordster's Soliloquy&lt;/color&gt; đạt 200/400/600 điểm, Qiuyuan lần lượt mở khóa &lt;color=Highlight&gt;Thus Spoke the Blade: Inkwash&lt;/color&gt;, &lt;color=Highlight&gt;Bamboo's Shade&lt;/color&gt; và &lt;color=Highlight&gt;Inksplash of Mind&lt;/color&gt;.</t>
+          <t>Qiuyuan hồi phục &lt;color=Highlight&gt;Độc Thoại Kiếm Khách&lt;/color&gt; thông qua Đòn Basic Attack Giai đoạn 3 và Dodge Counter Tránh. Khi &lt;color=Highlight&gt;Độc Thoại Kiếm Khách&lt;/color&gt; đạt 200/400/600 điểm, Qiuyuan lần lượt mở khóa &lt;color=Highlight&gt;Lưỡi Kiếm Lên Tiếng: Mực Tàu&lt;/color&gt;, &lt;color=Highlight&gt;Bóng Tre&lt;/color&gt; và &lt;color=Highlight&gt;Mực Tàu Tâm Trí&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25850,7 +25850,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Inksplash of Mind&lt;/color&gt;, Qiuyuan không thể hồi phục &lt;color=Highlight&gt;Swordster's Soliloquy&lt;/color&gt;, nhưng có thể tiêu hao &lt;color=Highlight&gt;Swordster's Soliloquy&lt;/color&gt; để tăng sát thương kỹ năng.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Mực Tâm Loang&lt;/color&gt;, Qiuyuan không thể hồi phục &lt;color=Highlight&gt;Độc Thoại Kiếm Khách&lt;/color&gt;, nhưng có thể tiêu hao &lt;color=Highlight&gt;Độc Thoại Kiếm Khách&lt;/color&gt; để tăng DMG kỹ năng.</t>
         </is>
       </c>
     </row>
@@ -25915,7 +25915,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Khi sử dụng Kỹ Năng Echo, Qiuyuan nhận được &lt;color=Highlight&gt;Flowing Panacea&lt;/color&gt;, sẽ được tiêu hao để tăng Tấn Công cho lần nhận &lt;color=Highlight&gt;Swordster's Soliloquy&lt;/color&gt; tiếp theo.</t>
+          <t>Khi sử dụng Kỹ Năng Tiếng Vọng, Qiuyuan nhận được &lt;color=Highlight&gt;Dược Lưu Chuyển&lt;/color&gt;, sẽ được tiêu hao để tăng ATK cho lần nhận &lt;color=Highlight&gt;Độc Thoại Kiếm Khách&lt;/color&gt; tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Qiuyuan uống từ bình tre của mình để hồi phục *Swordster's Soliloquy*. Khi đầy, Qiuyuan bước vào trạng thái &lt;color=Highlight&gt;Inksplash of Mind&lt;/color&gt; để gây thêm Sát Thương, đổi lại sẽ tiêu hao *Swordster's Soliloquy*.</t>
+          <t>Qiuyuan uống từ bình tre của mình để hồi phục *Độc Thoại Kiếm Khách*. Khi đầy, Qiuyuan bước vào trạng thái &lt;color=Highlight&gt;Mực Tàu Tâm Trí&lt;/color&gt; để gây thêm Sát Thương, đổi lại sẽ tiêu hao *Độc Thoại Kiếm Khách*.</t>
         </is>
       </c>
     </row>
@@ -26440,8 +26440,8 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Zani hồi phục Thanh Forte khi Resonators khác trong đội gây ra Spectro Frazzle.
-Khi kích hoạt Resonance Liberation, Zani bước vào trạng thái tăng cường. Trong trạng thái này, tiêu hao Thanh Forte để thực hiện các Basic Attack được nâng cấp.</t>
+          <t>Zani hồi phục Thanh Forte khi các Resonator khác trong đội gây ra Spectro Frazzle.
+Khi kích hoạt Resonance Liberation, Zani bước vào trạng thái tăng cường. Trong trạng thái này, tiêu hao Thanh Forte để thực hiện các Đòn Cơ Bản được nâng cấp.</t>
         </is>
       </c>
     </row>
@@ -26506,7 +26506,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Scissors Mode&lt;/color&gt;, tấn công để tích Năng Lượng Forte &lt;color=Highlight&gt;Ring of Chainsaw&lt;/color&gt;. Khi &lt;color=Highlight&gt;Ring of Chainsaw&lt;/color&gt; đầy, Chisa có thể sử dụng &lt;color=Highlight&gt;enhanced Resonance Skill&lt;/color&gt; và chuyển sang &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Kéo&lt;/color&gt;, tấn công để tích Năng Lượng Forte &lt;color=Highlight&gt;Vòng Cưa Xích&lt;/color&gt;. Khi &lt;color=Highlight&gt;Vòng Cưa Xích&lt;/color&gt; đầy, Chisa có thể sử dụng &lt;color=Highlight&gt;Resonance Skill được tăng cường&lt;/color&gt; và chuyển sang &lt;color=Highlight&gt;Chế Độ Cưa Xích&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26571,7 +26571,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;, các đòn tấn công sẽ tiêu hao Đồng Hồ Forte &lt;color=Highlight&gt;Ring of Chainsaw&lt;/color&gt; để tăng đáng kể hệ số sát thương của &lt;color=Highlight&gt;Sawring - Eradication&lt;/color&gt;.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Cưa Máy&lt;/color&gt;, các đòn tấn công sẽ tiêu hao Đồng Hồ Forte &lt;color=Highlight&gt;Ring of Chainsaw&lt;/color&gt; để tăng đáng kể hệ số DMG của &lt;color=Highlight&gt;Sawring - Eradication&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26636,7 +26636,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;, hệ số sát thương của các kỹ năng &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt; sẽ tăng đáng kể.</t>
+          <t>Sau khi sử dụng &lt;color=Highlight&gt;Giải Cộng Hưởng&lt;/color&gt;, hệ số DMG của các kỹ năng &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt; sẽ tăng đáng kể.</t>
         </is>
       </c>
     </row>
@@ -26701,7 +26701,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Scissors Mode&lt;/color&gt;, Chisa có thể tiêu hao Năng Lượng Forte &lt;color=Highlight&gt;Lifethread - Jetstream&lt;/color&gt; để thực hiện Dodge Special trên không khi sử dụng các kỹ năng nhất định.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Kéo&lt;/color&gt;, Chisa có thể tiêu hao Năng Lượng Forte &lt;color=Highlight&gt;Luồng Sinh Mệnh - Dòng Phản Lực&lt;/color&gt; để thực hiện Né Đặc Biệt trên không khi sử dụng các kỹ năng nhất định.</t>
         </is>
       </c>
     </row>
@@ -26768,9 +26768,9 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;, Đồng Hồ Forte &lt;color=Highlight&gt;Lifethread - Jetstream&lt;/color&gt; sẽ được thay thế bằng Đồng Hồ Forte &lt;color=Highlight&gt;Chainsaw Fever&lt;/color&gt;.
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Cưa Máy&lt;/color&gt;, Đồng Hồ Forte &lt;color=Highlight&gt;Lifethread - Jetstream&lt;/color&gt; sẽ được thay thế bằng Đồng Hồ Forte &lt;color=Highlight&gt;Chainsaw Fever&lt;/color&gt;.
 Khi Chisa ngừng tấn công một lúc, &lt;color=Highlight&gt;Chainsaw Fever&lt;/color&gt; sẽ dần cạn kiệt, nhưng nếu đánh trúng kẻ địch trong thời gian này sẽ làm mới lại.
-Khi &lt;color=Highlight&gt;Chainsaw Fever&lt;/color&gt; giảm về 0, Chisa sẽ thoát khỏi &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt; và chuyển sang &lt;color=Highlight&gt;Burnout State&lt;/color&gt;, trong đó Đồng Hồ Forte &lt;color=Highlight&gt;Ring of Chainsaw&lt;/color&gt; tiếp tục cạn kiệt.</t>
+Khi &lt;color=Highlight&gt;Chainsaw Fever&lt;/color&gt; giảm về 0, Chisa sẽ thoát khỏi &lt;color=Highlight&gt;Chế Độ Cưa Máy&lt;/color&gt; và chuyển sang &lt;color=Highlight&gt;Trạng Thái Kiệt Sức&lt;/color&gt;, trong đó Đồng Hồ Forte &lt;color=Highlight&gt;Ring of Chainsaw&lt;/color&gt; tiếp tục cạn kiệt.</t>
         </is>
       </c>
     </row>
@@ -26835,7 +26835,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Gây sát thương Resonance Liberation mạnh. Heal và tạo Khiên cho Resonators trong đội.</t>
+          <t>Gây DMG Resonance Liberation mạnh. Hồi phục và tạo Khiên cho các Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -26900,7 +26900,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Gây hiệu ứng Tai Họa Hỗn Loạn và giảm Phòng Ngự của mục tiêu. Kỹ Năng Kết Thúc tăng số tầng Status Tiêu Cực tối đa mục tiêu có thể nhận và cho phép Resonators trong đội bỏ qua Phòng Ngự của mục tiêu.</t>
+          <t>Gây hiệu ứng Havoc Bane và giảm Phòng Ngự của mục tiêu. Outro Skill tăng số tầng Trạng Thái Tiêu Cực tối đa mục tiêu có thể nhận và cho phép Resonator trong đội bỏ qua Phòng Ngự của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Resonance Skill đánh dấu mục tiêu. Một số kỹ năng của Chisa có thể kéo các mục tiêu đã đánh dấu về phía mình.</t>
+          <t>Kỹ năng Cộng Hưởng đánh dấu mục tiêu. Một số kỹ năng của Chisa có thể kéo các mục tiêu đã đánh dấu về phía mình.</t>
         </is>
       </c>
     </row>
@@ -27030,7 +27030,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Diễu Hành Sắc Màu - Basic Attack: Khi ở trong trạng thái &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để nhận &lt;color=Highlight&gt;Lumiflow&lt;/color&gt;.</t>
+          <t>Diễu Hành Sắc Màu - Basic Attack: Khi ở trong trạng thái &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để nhận &lt;color=Highlight&gt;Luồng Sáng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27095,7 +27095,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Bước Nhảy Đa Sắc: Khi có đủ &lt;color=Highlight&gt;Lumiflow&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy để tung chiêu &lt;color=Highlight&gt;Polychrome Leap&lt;/color&gt;, nhận 1 điểm &lt;color=Highlight&gt;True Color&lt;/color&gt; và gây hiệu ứng &lt;color=Highlight&gt;Photochromic Flux&lt;/color&gt; lên mục tiêu khi trúng đích.</t>
+          <t>Bước Nhảy Đa Sắc: Khi có đủ &lt;color=Highlight&gt;Dòng Lưu Quang&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy để tung chiêu &lt;color=Highlight&gt;Bước Nhảy Đa Sắc&lt;/color&gt;, nhận 1 điểm &lt;color=Highlight&gt;Màu Chân Thực&lt;/color&gt; và gây hiệu ứng &lt;color=Highlight&gt;Dòng Phổ Quang&lt;/color&gt; lên mục tiêu khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Lynae có thể chuyển đổi giữa &lt;color=Highlight&gt;Resonance Mode - Tune Rupture&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Mode - Tune Strain&lt;/color&gt;, cho phép cô gây &lt;color=Highlight&gt;Tune Rupture - Shifting&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt; lên mục tiêu tương ứng.</t>
+          <t>Lynae có thể chuyển đổi giữa &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Đứt Giai Điệu&lt;/color&gt; và &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Căng Giai Điệu&lt;/color&gt;, cho phép cô gây &lt;color=Highlight&gt;Đứt Giai Điệu - Dịch Chuyển&lt;/color&gt; hoặc &lt;color=Highlight&gt;Căng Giai Điệu - Dịch Chuyển&lt;/color&gt; lên mục tiêu tương ứng.</t>
         </is>
       </c>
     </row>
@@ -27225,7 +27225,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Khi sử dụng &lt;color=Highlight&gt;Prismatic Overblast&lt;/color&gt; và &lt;color=Highlight&gt;Visual Impact&lt;/color&gt;, tất cả Resonators trong đội sẽ nhận được hiệu ứng tăng cường.</t>
+          <t>Khi sử dụng &lt;color=Highlight&gt;Vụ Nổ Đa Sắc&lt;/color&gt; và &lt;color=Highlight&gt;Cú Đánh Thị Giác&lt;/color&gt;, tất cả Resonator trong đội sẽ nhận được hiệu ứng tăng cường.</t>
         </is>
       </c>
     </row>
@@ -27290,7 +27290,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Outro Skill ban cho Resonator tiếp theo &lt;color=Highlight&gt;Tất cả DMG Amplification&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Liberation DMG Amplification&lt;/color&gt;.</t>
+          <t>Kỹ Năng Outro ban cho Resonator tiếp theo &lt;color=Highlight&gt;Khuếch Đại Sát Thương Toàn Bộ&lt;/color&gt; và &lt;color=Highlight&gt;Khuếch Đại Sát Thương Resonance Liberation&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27356,8 +27356,8 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Kích hoạt Intro Skill sẽ hồi phục Thanh Forte.
-Tấn công mục tiêu bằng Normal Attack và Vining Waltz sẽ tiêu hao Thanh Forte.</t>
+          <t>Kích hoạt Kỹ Năng Khởi Động sẽ hồi phục Thanh Forte.
+Tấn công mục tiêu bằng Đòn Thường và Vining Waltz sẽ tiêu hao Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -27422,7 +27422,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy, kích hoạt Ephemeral của Forte Circuit và bước vào Chế Độ Đâm Chồi. Nhận thêm hệ số nhân sát thương khi ở Chế Độ Đâm Chồi.</t>
+          <t>Khi Concerto Energy đầy, kích hoạt Ephemeral của Forte Circuit và bước vào Chế Độ Đâm Chồi. Nhận thêm hệ số nhân DMG khi ở Chế Độ Đâm Chồi.</t>
         </is>
       </c>
     </row>
@@ -27617,7 +27617,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Giới Thiệu, Resonance Skill và Resonance Liberation sẽ hồi phục Trance. Khi Trance chưa cạn, thực hiện Heavy Attack sẽ đưa Cantarella vào trạng thái tăng cường.</t>
+          <t>Kích hoạt Kỹ Năng Giới Thiệu, Resonance Skill và Resonance Liberation sẽ hồi phục Trance. Khi Trance chưa cạn, thực hiện Đòn Heavy Attack sẽ đưa Cantarella vào trạng thái tăng cường.</t>
         </is>
       </c>
     </row>
@@ -27682,7 +27682,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Khi Cantarella ở trạng thái tăng cường, đánh trúng mục tiêu bằng Basic Attack sẽ hồi phục Điểm Rùng Mình. Khi Điểm Rùng Mình đạt 3, kỹ năng Resonance được tăng cường sẽ sẵn sàng.</t>
+          <t>Khi Cantarella ở trạng thái tăng cường, đánh trúng mục tiêu bằng Đòn Basic Attack sẽ hồi phục Điểm Rùng Mình. Khi Điểm Rùng Mình đạt 3, kỹ năng Cộng Hưởng được tăng cường sẽ sẵn sàng.</t>
         </is>
       </c>
     </row>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Sử dụng Basic Attack Stage 3 hoặc Resonance Skill sẽ kích hoạt đòn tiếp nối bằng Basic Attack Nâng Cao hoặc Resonance Skill Nâng Cao và nhận các loại Forte Gauge khác nhau.</t>
+          <t>Sử dụng Đòn Basic Attack Giai Đoạn 3 hoặc Resonance Skill sẽ kích hoạt đòn tiếp nối bằng Đòn Basic Attack Nâng Cao hoặc Resonance Skill Nâng Cao và nhận các loại Forte Gauge khác nhau.</t>
         </is>
       </c>
     </row>
@@ -27812,7 +27812,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Thu thập 6 điểm Đồng Bộ Năng Lực để tung ra Heavy Attack Cường Hóa, gây sát thương khủng khiếp và mở khóa Resonance Liberation.</t>
+          <t>Thu thập 6 điểm Đồng Bộ Năng Lực để tung ra Đòn Heavy Attack Cường Hóa, gây sát thương khủng khiếp và mở khóa Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -28007,7 +28007,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Echo của Resonators trong đội sẽ gây một lượng lớn Sát Thương Resonance Skill và Sát Thương Kỹ Năng Echo.</t>
+          <t>Kích hoạt Kỹ Năng Echo của các Resonator trong đội sẽ gây một lượng lớn Sát Thương Resonance Skill và Sát Thương Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -28072,7 +28072,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Các Skills Chuỗi khác nhau sẽ cung cấp loại Forte Gauge khác nhau, cho phép sử dụng các bộ chiêu thức đa dạng trong trạng thái tăng cường.</t>
+          <t>Các Kỹ Năng Chuỗi khác nhau sẽ cung cấp loại Forte Gauge khác nhau, cho phép sử dụng các bộ chiêu thức đa dạng trong trạng thái tăng cường.</t>
         </is>
       </c>
     </row>
@@ -28137,7 +28137,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Kỹ Năng Hồi Kết khuếch đại Havoc DMG và Sát Thương Heavy Attack của Resonator kế tiếp.</t>
+          <t>Kỹ Năng Hồi Kết khuếch đại Sát Thương Havoc và Sát Thương Đòn Heavy Attack của Resonator kế tiếp.</t>
         </is>
       </c>
     </row>
@@ -28332,7 +28332,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Sát Thương Nhấn Giữa Không Trung</t>
+          <t>Sát Thương khi Nhấn trên không</t>
         </is>
       </c>
     </row>
@@ -28397,7 +28397,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Sát Thương Phép Thuật Heavy Attack</t>
+          <t>HA - Sát Thương Phép Thuật</t>
         </is>
       </c>
     </row>
@@ -28462,7 +28462,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Concerto Regen Thiên Tài Bất Chợt</t>
+          <t>Hồi Phục Giao Hưởng Nét Thiên Tài</t>
         </is>
       </c>
     </row>
@@ -28527,7 +28527,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Changli hồi phục Forte Gauge khi nhảy hoặc đánh trúng mục tiêu bằng Basic Attack trong True Sight, hoặc khi sử dụng Resonance Liberation.</t>
+          <t>Changli hồi phục Forte Gauge khi nhảy hoặc đánh trúng mục tiêu bằng Đòn Basic Attack trong True Sight, hoặc khi sử dụng Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -28592,7 +28592,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Khi Thanh Forte đầy, giữ Basic Attack để thực hiện Heavy Attack được tăng cường.</t>
+          <t>Khi Thanh Forte đầy, giữ Đòn Basic Attack để thực hiện Đòn Tấn Công Mạnh được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -28657,7 +28657,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Hồi phục Thanh Forte ở trạng thái bình thường khi Resonance Skill trúng mục tiêu. Kích hoạt Heavy Attack Được Tăng Cường khi Thanh Forte đầy</t>
+          <t>Hồi phục Thanh Forte ở trạng thái bình thường khi Resonance Skill trúng mục tiêu. Kích hoạt Đòn Heavy Attack Được Tăng Cường khi Thanh Forte đầy</t>
         </is>
       </c>
     </row>
@@ -28722,7 +28722,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Hồi phục Thanh Forte khi Basic Attack trúng mục tiêu. Kích hoạt Resonance Liberation khi Thanh Forte đầy</t>
+          <t>Hồi phục Thanh Forte khi Đòn Basic Attack trúng mục tiêu. Kích hoạt Resonance Liberation khi Thanh Forte đầy</t>
         </is>
       </c>
     </row>
@@ -28787,7 +28787,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Hồi phục Thanh Forte khi Basic Attack, Heavy Attack hoặc Resonance Skill trúng mục tiêu</t>
+          <t>Hồi phục Thanh Forte khi Đòn Basic Attack, Đòn Heavy Attack hoặc Resonance Skill trúng mục tiêu</t>
         </is>
       </c>
     </row>
@@ -28852,7 +28852,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Giữ Basic Attack để thi triển Đòn Attack được tăng cường khi Thanh Forte đầy</t>
+          <t>Giữ Đòn Basic Attack để thi triển Đòn Tấn Công được tăng cường khi Thanh Forte đầy</t>
         </is>
       </c>
     </row>
@@ -29047,7 +29047,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Thanh Tần Số của Jinhsi được phục hồi khi Resonators gây Sát Thương Thuộc Tính hoặc Sát Thương Attack Phối Hợp.</t>
+          <t>Thanh Tần Số của Jinhsi được phục hồi khi Resonator gây Sát Thương Thuộc Tính hoặc Sát Thương Tấn Công Phối Hợp.</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill hoặc đánh trúng kẻ địch bằng Normal Attack sẽ hồi phục Thanh Forte.</t>
+          <t>Kích hoạt Resonance Skill hoặc đánh trúng kẻ địch bằng Đòn Normal Attack sẽ hồi phục Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Hồi phục Thanh Forte khi Basic Attack 4, Heavy Attack phái sinh, Resonance Skill hoặc Intro Skill trúng mục tiêu</t>
+          <t>Hồi phục Thanh Forte khi Đòn Basic Attack 4, Đòn Heavy Attack phái sinh, Resonance Skill hoặc Kỹ Năng Khởi Động trúng mục tiêu</t>
         </is>
       </c>
     </row>
@@ -29437,7 +29437,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Hồi phục Thanh Forte khi Basic Attack hoặc Đòn Mid-air Attack trúng mục tiêu thông qua "Sương Mù"</t>
+          <t>Hồi phục Thanh Forte khi Đòn Basic Attack hoặc Đòn Tấn Công Giữa Không trúng mục tiêu thông qua "Sương Mù"</t>
         </is>
       </c>
     </row>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Tạo ra Đạn Mist để tấn công mục tiêu khi đi qua "Mist".</t>
+          <t>Tạo ra Đạn Sương mù để tấn công mục tiêu khi đi qua "Sương mù".</t>
         </is>
       </c>
     </row>
@@ -29567,7 +29567,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Normal Attack và Intro Skill hồi phục Thanh Forte khi trúng đích</t>
+          <t>Đòn Normal Attack và Kỹ Năng Khởi Động hồi phục Thanh Forte khi trúng đích</t>
         </is>
       </c>
     </row>
@@ -29762,7 +29762,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Normal Attack, Resonance Skill và Intro Skill hồi phục Thanh Forte khi trúng mục tiêu</t>
+          <t>Normal Attack, Resonance Skill và Kỹ Năng Khởi Động hồi phục Thanh Forte khi trúng mục tiêu</t>
         </is>
       </c>
     </row>
@@ -29892,7 +29892,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Tích lũy 1 Đồng Hồ Forte cho Basic Attack V, Resonance Skill hoặc Intro Skill khi trúng mục tiêu, tối đa 4</t>
+          <t>Tích lũy 1 Đồng Hồ Forte cho Đòn Cơ Bản V, Resonance Skill hoặc Kỹ Năng Khởi Động khi trúng mục tiêu, tối đa 4</t>
         </is>
       </c>
     </row>
@@ -30022,7 +30022,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Normal Attack hồi phục Thanh Forte và tạo ra Lõi Suy Sụp khi trúng đích</t>
+          <t>Đòn Normal Attack hồi phục Thanh Forte và tạo ra Lõi Suy Sụp khi trúng đích</t>
         </is>
       </c>
     </row>
@@ -30087,7 +30087,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Khi Thanh Forte đầy, giữ Button Normal Attack hoặc thực hiện Đòn Lao Xuống để tung ra Đòn Attack Được Tăng Cường và chuyển hóa tất cả Lõi Suy Sụp thành Bướm Sao Flare.</t>
+          <t>Khi Thanh Forte đầy, giữ Nút Normal Attack hoặc thực hiện Đòn Lao Xuống để tung ra Đòn Tấn Công Được Tăng Cường và chuyển hóa tất cả Lõi Suy Sụp thành Bướm Sao Flare.</t>
         </is>
       </c>
     </row>
@@ -30152,7 +30152,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Khi bị tấn công hoặc khi Resonance Skill tạo khiên và Basic Attack 4 trúng mục tiêu, khiên sẽ chuyển hóa thành Đồng Hồ Forte.</t>
+          <t>Khi bị tấn công hoặc khi Resonance Skill tạo khiên và Đòn Basic Attack 4 trúng mục tiêu, khiên sẽ chuyển hóa thành Đồng Hồ Forte.</t>
         </is>
       </c>
     </row>
@@ -30412,7 +30412,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Hồi phục Thanh Forte khi Basic Attack trúng mục tiêu hoặc khi Intro Skill, Resonance Skill được kích hoạt</t>
+          <t>Hồi phục Thanh Forte khi Đòn Basic Attack trúng mục tiêu hoặc khi Kỹ Năng Khởi Động, Resonance Skill được kích hoạt</t>
         </is>
       </c>
     </row>
@@ -30542,7 +30542,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Khi ở trong &lt;color=Highlight&gt;Resonance Mode - Tune Rupture&lt;/color&gt;, gây thêm Sát Thương Tune Break Hủy. Chế độ này ưu tiên sát thương đơn mục tiêu. Đội của cậu càng có nhiều Resonators có khả năng phản ứng với &lt;color=Highlight&gt;Tune Rupture - Interfered&lt;/color&gt;, Aemeath càng gây nhiều sát thương hơn.</t>
+          <t>Khi ở trong &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Đoạn Tần Phá Hủy&lt;/color&gt;, gây thêm Sát Thương Đoạn Tần Phá Hủy. Chế độ này ưu tiên DMG đơn mục tiêu. Đội của cậu càng có nhiều Resonator có khả năng phản ứng với &lt;color=Highlight&gt;Đoạn Tần Phá Hủy - Nhiễu Loạn&lt;/color&gt;, Aemeath càng gây nhiều DMG hơn.</t>
         </is>
       </c>
     </row>
@@ -30607,7 +30607,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Trong &lt;color=Highlight&gt;Resonance Mode - Fusion Burst&lt;/color&gt;, Aemeath sẽ gây hiệu ứng &lt;color=Highlight&gt;Fusion Burst&lt;/color&gt;. Chế độ này giải phóng tiềm năng sát thương diện rộng của cô, cho phép gây nhiều sát thương hơn bằng cách thường xuyên áp dụng &lt;color=Highlight&gt;Fusion Burst&lt;/color&gt;.</t>
+          <t>Trong &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Bùng Nổ Hợp Thể&lt;/color&gt;, Aemeath sẽ gây hiệu ứng &lt;color=Highlight&gt;Bùng Nổ Hợp Thể&lt;/color&gt;. Chế độ này giải phóng tiềm năng DMG diện rộng của cô, cho phép gây nhiều DMG hơn bằng cách thường xuyên áp dụng &lt;color=Highlight&gt;Bùng Nổ Hợp Thể&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30672,7 +30672,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Thiên Lệnh Cú Đổ: Chung Kết: khi &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Rate&lt;/color&gt; đạt tối đa, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {1} hoặc {0}.</t>
+          <t>Thiên Lệnh Cú Đổ: Chung Kết: khi &lt;color=Highlight&gt;Tỷ Lệ Đồng Bộ&lt;/color&gt; và &lt;color=Highlight&gt;Tỷ Lệ Cộng Hưởng&lt;/color&gt; đạt tối đa, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {1} hoặc {0}.</t>
         </is>
       </c>
     </row>
@@ -30737,7 +30737,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} {0}+{0}+{0}+{0} trên mặt đất hoặc {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0}+{0}/Nhảy+{0}/Nhảy trên không để kích hoạt Resonance Skill &lt;color=Highlight&gt;Aureole of Execution&lt;/color&gt;. Sau khi kích hoạt, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {1} để thi triển Resonance Skill &lt;color=Highlight&gt;Aureole of Execution&lt;/color&gt;.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} {0}+{0}+{0}+{0} trên mặt đất hoặc {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0}+{0}/Nhảy+{0}/Nhảy trên không để kích hoạt Resonance Skill &lt;color=Highlight&gt;Aureole of Execution&lt;/color&gt;. Sau khi kích hoạt, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {1} để thi triển Resonance Skill &lt;color=Highlight&gt;Aureole of Execution&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30867,7 +30867,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Heavy Attack: Giữ {0} trên mặt đất và tiêu hao Thể Lực để bật lên không trung.</t>
+          <t>Đòn Heavy Attack: Giữ {0} trên mặt đất và tiêu hao STA để bật lên không trung.</t>
         </is>
       </c>
     </row>
@@ -30932,7 +30932,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Radiant Reave: {Cus:Ipt,Touch=Touch PC=press Gamepad=press} Dodge trên không để thực hiện Dodge. Lơ lửng trong không trung một lát rồi phóng lưỡi kiếm xoay tròn tấn công mục tiêu.</t>
+          <t>Radiant Reave: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Né trên không để thực hiện né tránh. Lơ lửng trong không trung một lát rồi phóng lưỡi kiếm xoay tròn tấn công mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -31062,7 +31062,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Bằng cách gây ra và phản ứng với &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt;, Luuk Herssen gây thêm Total Sát Thương.</t>
+          <t>Bằng cách gây ra và phản ứng với &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt;, Luuk Herssen gây thêm Tổng Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Nhờ Tune Break Boost từ Resonators khác trong đội, Luuk Herssen nhận được lượng Sát Thương Khuếch Đại đáng kể.</t>
+          <t>Nhờ Tune Break Boost từ các Resonator khác trong đội, Luuk Herssen nhận được lượng Sát Thương Khuếch Đại đáng kể.</t>
         </is>
       </c>
     </row>
@@ -31257,7 +31257,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Enhanced Heavy Attack&lt;/color&gt; mang lại nhiều hiệu ứng như Lực Kéo và Trì Trệ, giúp thích ứng với các tình huống chiến đấu khác nhau.</t>
+          <t>&lt;color=Highlight&gt;Đòn Heavy Attack Cường Hóa&lt;/color&gt; mang lại nhiều hiệu ứng như Lực Kéo và Trì Trệ, giúp thích ứng với các tình huống chiến đấu khác nhau.</t>
         </is>
       </c>
     </row>
@@ -31322,7 +31322,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Các Resonators trong đội hồi Phục Thanh Năng Sigrika khi sử dụng Skills Echo, từ đó giúp cô nhận được DMG Amplification đáng kể.</t>
+          <t>Các Resonator trong đội hồi Phục Thanh Năng Sigrika khi sử dụng Kỹ Năng Echo, từ đó giúp cô nhận được Khuếch Đại Sát Thương đáng kể.</t>
         </is>
       </c>
     </row>
@@ -31387,7 +31387,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Tăng thưởng Sát Thương cho tất cả Resonators trong đội.</t>
+          <t>Tăng thưởng Sát Thương cho tất cả Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -31452,7 +31452,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Resonance Mode - Fusion Burst&lt;/color&gt;, Denia có thể gây &lt;color=Highlight&gt;Fusion Burst&lt;/color&gt; thường xuyên hơn và tăng sát thương cho đội Bùng Nổ Fusion.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Bùng Nổ Fusion&lt;/color&gt;, Denia có thể gây &lt;color=Highlight&gt;Bùng Nổ Fusion&lt;/color&gt; thường xuyên hơn và tăng DMG cho đội Bùng Nổ Fusion.</t>
         </is>
       </c>
     </row>
@@ -31517,7 +31517,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Resonance Mode - Tune Strain&lt;/color&gt;, Denia có thể gây &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt;, đặt lại thời gian &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt;, tăng nhanh &lt;color=Highlight&gt;Off-Tune Level&lt;/color&gt; của mục tiêu và tổng thể tăng sát thương của đội hình Phản Ứng Giai Tune Méo Mó.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Cộng Hưởng - Giai Điệu Méo Mó&lt;/color&gt;, Denia có thể gây &lt;color=Highlight&gt;Giai Điệu Méo Mó - Dịch Chuyển&lt;/color&gt;, đặt lại thời gian &lt;color=Highlight&gt;Giai Điệu Méo Mó - Giao Thoa&lt;/color&gt;, tăng nhanh &lt;color=Highlight&gt;Mức Độ Lệch Giai Điệu&lt;/color&gt; của mục tiêu và tổng thể tăng DMG của đội hình Phản Ứng Giai Điệu Méo Mó.</t>
         </is>
       </c>
     </row>
@@ -31582,7 +31582,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Hủy Diệt - Hình Thái Suy Thoái: &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt; trong &lt;color=Highlight&gt;Breakdown Form&lt;/color&gt;. Khi giữ &lt;color=Highlight&gt;Dark Cores&lt;/color&gt;, {0} + {0} hoặc {0} + {1}</t>
+          <t>Hủy Diệt - Hình Thái Suy Thoái: &lt;color=Highlight&gt;Resonance Skill Nâng Cao&lt;/color&gt; trong &lt;color=Highlight&gt;Hình Thái Suy Thoái&lt;/color&gt;. Khi giữ &lt;color=Highlight&gt;Lõi Hắc Ám&lt;/color&gt;, {0} + {0} hoặc {0} + {1}</t>
         </is>
       </c>
     </row>
@@ -31647,7 +31647,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Hồi Kết - Hình Thái Sụp Đổ: &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; trong &lt;color=Highlight&gt;Breakdown Form&lt;/color&gt;. Khi &lt;color=Highlight&gt;Conformal Charge&lt;/color&gt; đầy, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0}</t>
+          <t>Hồi Kết - Hình Thái Sụp Đổ: &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; trong &lt;color=Highlight&gt;Hình Thái Sụp Đổ&lt;/color&gt;. Khi &lt;color=Highlight&gt;Điện Tích Tuân Thủ&lt;/color&gt; đầy, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0}</t>
         </is>
       </c>
     </row>
@@ -31712,7 +31712,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Heavy Attack - Mảnh Băng Sương: Hiện Thân: Khi ở trạng thái &lt;color=Highlight&gt;Present Self&lt;/color&gt;, khi &lt;color=Highlight&gt;Dedication&lt;/color&gt; đạt 300 điểm, giữ {0}.</t>
+          <t>Tấn Công Mạnh - Mảnh Băng Sương: Hiện Thân: Khi ở trạng thái &lt;color=Highlight&gt;Hiện Thân&lt;/color&gt;, khi &lt;color=Highlight&gt;Cống Hiến&lt;/color&gt; đạt 300 điểm, giữ {0}.</t>
         </is>
       </c>
     </row>
@@ -31777,7 +31777,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Nội Quan: Khi ở trạng thái &lt;color=Highlight&gt;Present Self&lt;/color&gt;, mở khóa sau khi thi triển &lt;color=Highlight&gt;Heavy Attack - Frost Splinter: Present Self&lt;/color&gt;. Khi mở khóa, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0}.</t>
+          <t>Nội Quan: Khi ở trạng thái &lt;color=Highlight&gt;Bản Ngã Hiện Tại&lt;/color&gt;, mở khóa sau khi thi triển &lt;color=Highlight&gt;Đòn Heavy Attack - Mảnh Băng: Bản Ngã Hiện Tại&lt;/color&gt;. Khi mở khóa, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0}.</t>
         </is>
       </c>
     </row>
@@ -31842,7 +31842,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Basic Attack - Iai: Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt; và trong &lt;color=Highlight&gt;Iai Stance&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0}.</t>
+          <t>Basic Attack - Iai: Khi ở trạng thái &lt;color=Highlight&gt;Tự Dự Báo&lt;/color&gt; và trong &lt;color=Highlight&gt;Tư Thế Iai&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0}.</t>
         </is>
       </c>
     </row>
@@ -31907,7 +31907,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Heavy Attack - Bitterfrost: Tự Kết Tội: Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, với 3 lớp &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt;, giữ {0}.</t>
+          <t>Đòn Tấn Công Mạnh - Bitterfrost: Tự Kết Tội: Khi ở trạng thái &lt;color=Highlight&gt;Tự Kết Tội&lt;/color&gt;, với 3 lớp &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt;, giữ {0}.</t>
         </is>
       </c>
     </row>
@@ -31972,7 +31972,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Giải Phóng Kiếm: Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, nếu Resonance Energy đầy đủ, giữ {0} để vào trạng thái nạp, thả {0} để thi triển.</t>
+          <t>Giải Phóng Kiếm: Khi ở trạng thái &lt;color=Highlight&gt;Bản Ngã Đã Định&lt;/color&gt;, nếu Resonance Energy đầy đủ, giữ {0} để vào trạng thái nạp, thả {0} để thi triển.</t>
         </is>
       </c>
     </row>
@@ -32167,7 +32167,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Tích lũy và tiêu thụ &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Foreclaiming: Blade Liberation&lt;/color&gt;. Càng tiêu thụ nhiều, sát thương càng cao.</t>
+          <t>Tích lũy và tiêu thụ &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Foreclaiming: Blade Liberation&lt;/color&gt;. Càng tiêu thụ nhiều, DMG càng cao.</t>
         </is>
       </c>
     </row>
@@ -32232,7 +32232,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Giữ Basic Attack để thi triển Heavy Attack và vào trạng thái tăng cường khi Thanh Forte đầy</t>
+          <t>Giữ Đòn Basic Attack để thi triển Đòn Tấn Công Mạnh và vào trạng thái tăng cường khi Thanh Forte đầy</t>
         </is>
       </c>
     </row>
@@ -32297,7 +32297,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Mở khóa khi kỹ năng tiên quyết đạt Cấp 1</t>
+          <t>Mở khóa khi kỹ năng điều kiện đạt Cấp 1</t>
         </is>
       </c>
     </row>
@@ -32362,7 +32362,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Mở khóa khi kỹ năng tiên quyết đạt Hạng 2</t>
+          <t>Mở khóa khi kỹ năng điều kiện đạt Hạng 2</t>
         </is>
       </c>
     </row>
@@ -32427,7 +32427,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Mở khóa khi kỹ năng tiên quyết đạt Hạng 2</t>
+          <t>Mở khóa khi kỹ năng điều kiện đạt Hạng 2</t>
         </is>
       </c>
     </row>
@@ -32492,7 +32492,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Mở khóa khi kỹ năng tiên quyết đạt Cấp 1</t>
+          <t>Mở khóa khi kỹ năng điều kiện đạt Cấp 1</t>
         </is>
       </c>
     </row>
@@ -32557,7 +32557,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Mở khóa khi kỹ năng tiên quyết đạt Hạng 2</t>
+          <t>Mở khóa khi kỹ năng điều kiện đạt Hạng 2</t>
         </is>
       </c>
     </row>
@@ -32622,7 +32622,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -32687,7 +32687,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -32752,7 +32752,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -32882,7 +32882,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 5</t>
+          <t>Sát Thương Giai Đoạn 5</t>
         </is>
       </c>
     </row>
@@ -33012,7 +33012,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Sát Thương Lao Xuống Hào Hùng</t>
+          <t>Sát Thương Lao Xuống Vinh Quang</t>
         </is>
       </c>
     </row>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -33142,7 +33142,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -33337,7 +33337,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -33467,7 +33467,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Sát Thương Đấm Mạnh</t>
+          <t>Sát Thương Đấm Cuồng Nộ</t>
         </is>
       </c>
     </row>
@@ -33597,7 +33597,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -33662,7 +33662,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Thời Gian Hăng Hái Của Sư Tử</t>
+          <t>Thời Gian Hiệu Lực Sức Mạnh Sư Tử</t>
         </is>
       </c>
     </row>
@@ -33857,7 +33857,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -33922,7 +33922,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -33987,7 +33987,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -34182,7 +34182,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Sát Thương Lang Thang Núi</t>
+          <t>Sát Thương Kẻ Lang Thang Vùng Núi</t>
         </is>
       </c>
     </row>
@@ -34247,7 +34247,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Sát Thương Bổ Sung Lang Thang Núi</t>
+          <t>Sát Thương Bổ Sung Kẻ Lang Thang Vùng Núi</t>
         </is>
       </c>
     </row>
@@ -34312,7 +34312,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Sát Thương Đá Bão Táp</t>
+          <t>Sát Thương Đòn Đá Bão Tố</t>
         </is>
       </c>
     </row>
